--- a/NODELibrary/Data/Materialdata.xlsx
+++ b/NODELibrary/Data/Materialdata.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANDREA~1.NOD\AppData\Local\Temp\com.maplesoft\NODELibrary-89a5ca95-c122112a\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\NODEMaple\NODELibrary\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56B9C34-7C75-40C7-AB7F-6D4D4C969952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="18240" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LESMEG" sheetId="5" r:id="rId1"/>
-    <sheet name="betong" sheetId="4" r:id="rId2"/>
+    <sheet name="concrete" sheetId="4" r:id="rId2"/>
     <sheet name="steel" sheetId="6" r:id="rId3"/>
     <sheet name="tre" sheetId="3" r:id="rId4"/>
     <sheet name="limtre" sheetId="1" r:id="rId5"/>
@@ -21,10 +22,21 @@
     <sheet name="softwood tension tests" sheetId="7" r:id="rId7"/>
     <sheet name="hardwood" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -618,7 +630,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -740,7 +752,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -748,9 +760,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -783,14 +792,14 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -836,7 +845,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
@@ -850,10 +859,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -862,7 +868,7 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -871,28 +877,24 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -900,7 +902,7 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1185,7 +1187,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:B8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1213,1020 +1215,1020 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="11.42578125" style="34"/>
-    <col min="9" max="9" width="11.42578125" style="35"/>
-    <col min="10" max="12" width="11.42578125" style="34"/>
-    <col min="13" max="13" width="11.42578125" style="35"/>
-    <col min="14" max="16" width="11.42578125" style="34"/>
+    <col min="1" max="1" width="16.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="11.42578125" style="33"/>
+    <col min="9" max="9" width="11.42578125" style="34"/>
+    <col min="10" max="12" width="11.42578125" style="33"/>
+    <col min="13" max="13" width="11.42578125" style="34"/>
+    <col min="14" max="16" width="11.42578125" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="L1" s="31" t="s">
+      <c r="L1" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="M1" s="31" t="s">
+      <c r="M1" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="N1" s="31" t="s">
+      <c r="N1" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="O1" s="32" t="s">
+      <c r="O1" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="P1" s="32" t="s">
+      <c r="P1" s="31" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="C2" s="18">
+      <c r="C2" s="17">
         <v>10</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="17">
         <v>12</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="17">
         <v>20</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="17">
         <v>25</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="17">
         <v>28</v>
       </c>
-      <c r="F3" s="33">
+      <c r="F3" s="32">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G3" s="33">
+      <c r="G3" s="32">
         <v>1.5</v>
       </c>
-      <c r="H3" s="33">
+      <c r="H3" s="32">
         <v>2.9</v>
       </c>
-      <c r="I3" s="33">
+      <c r="I3" s="32">
         <v>30</v>
       </c>
-      <c r="J3" s="33">
+      <c r="J3" s="32">
         <v>2</v>
       </c>
-      <c r="K3" s="33">
+      <c r="K3" s="32">
         <v>3.5</v>
       </c>
-      <c r="L3" s="33">
+      <c r="L3" s="32">
         <v>2</v>
       </c>
-      <c r="M3" s="33">
+      <c r="M3" s="32">
         <v>3.5</v>
       </c>
-      <c r="N3" s="33">
+      <c r="N3" s="32">
         <v>2</v>
       </c>
-      <c r="O3" s="33">
+      <c r="O3" s="32">
         <v>1.75</v>
       </c>
-      <c r="P3" s="33">
+      <c r="P3" s="32">
         <v>3.5</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="17">
         <v>25</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="17">
         <v>30</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="17">
         <v>33</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="32">
         <v>2.6</v>
       </c>
-      <c r="G4" s="33">
+      <c r="G4" s="32">
         <v>1.8</v>
       </c>
-      <c r="H4" s="33">
+      <c r="H4" s="32">
         <v>3.3</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="32">
         <v>31</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="32">
         <v>2.1</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="32">
         <v>3.5</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="32">
         <v>2</v>
       </c>
-      <c r="M4" s="33">
+      <c r="M4" s="32">
         <v>3.5</v>
       </c>
-      <c r="N4" s="33">
+      <c r="N4" s="32">
         <v>2</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="32">
         <v>1.75</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="32">
         <v>3.5</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="17">
         <v>30</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="17">
         <v>37</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="17">
         <v>38</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="32">
         <v>2.9</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5" s="32">
         <v>2</v>
       </c>
-      <c r="H5" s="33">
+      <c r="H5" s="32">
         <v>3.8</v>
       </c>
-      <c r="I5" s="33">
+      <c r="I5" s="32">
         <v>33</v>
       </c>
-      <c r="J5" s="33">
+      <c r="J5" s="32">
         <v>2.2000000000000002</v>
       </c>
-      <c r="K5" s="33">
+      <c r="K5" s="32">
         <v>3.5</v>
       </c>
-      <c r="L5" s="33">
+      <c r="L5" s="32">
         <v>2</v>
       </c>
-      <c r="M5" s="33">
+      <c r="M5" s="32">
         <v>3.5</v>
       </c>
-      <c r="N5" s="33">
+      <c r="N5" s="32">
         <v>2</v>
       </c>
-      <c r="O5" s="33">
+      <c r="O5" s="32">
         <v>1.75</v>
       </c>
-      <c r="P5" s="33">
+      <c r="P5" s="32">
         <v>3.5</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="17">
         <v>35</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="17">
         <v>45</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="17">
         <v>43</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="32">
         <v>3.2</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6" s="32">
         <v>2.2000000000000002</v>
       </c>
-      <c r="H6" s="33">
+      <c r="H6" s="32">
         <v>4.2</v>
       </c>
-      <c r="I6" s="33">
+      <c r="I6" s="32">
         <v>34</v>
       </c>
-      <c r="J6" s="33">
+      <c r="J6" s="32">
         <v>2.25</v>
       </c>
-      <c r="K6" s="33">
+      <c r="K6" s="32">
         <v>3.5</v>
       </c>
-      <c r="L6" s="33">
+      <c r="L6" s="32">
         <v>2</v>
       </c>
-      <c r="M6" s="33">
+      <c r="M6" s="32">
         <v>3.5</v>
       </c>
-      <c r="N6" s="33">
+      <c r="N6" s="32">
         <v>2</v>
       </c>
-      <c r="O6" s="33">
+      <c r="O6" s="32">
         <v>1.75</v>
       </c>
-      <c r="P6" s="33">
+      <c r="P6" s="32">
         <v>3.5</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="17">
         <v>45</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <v>55</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="17">
         <v>53</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="32">
         <v>3.8</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="32">
         <v>2.7</v>
       </c>
-      <c r="H7" s="33">
+      <c r="H7" s="32">
         <v>4.9000000000000004</v>
       </c>
-      <c r="I7" s="33">
+      <c r="I7" s="32">
         <v>36</v>
       </c>
-      <c r="J7" s="33">
+      <c r="J7" s="32">
         <v>2.4</v>
       </c>
-      <c r="K7" s="33">
+      <c r="K7" s="32">
         <v>3.5</v>
       </c>
-      <c r="L7" s="33">
+      <c r="L7" s="32">
         <v>2</v>
       </c>
-      <c r="M7" s="33">
+      <c r="M7" s="32">
         <v>3.5</v>
       </c>
-      <c r="N7" s="33">
+      <c r="N7" s="32">
         <v>2</v>
       </c>
-      <c r="O7" s="33">
+      <c r="O7" s="32">
         <v>1.75</v>
       </c>
-      <c r="P7" s="33">
+      <c r="P7" s="32">
         <v>3.5</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="17">
         <v>55</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <v>67</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="17">
         <v>63</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="32">
         <v>4.2</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="32">
         <v>3</v>
       </c>
-      <c r="H8" s="33">
+      <c r="H8" s="32">
         <v>5.5</v>
       </c>
-      <c r="I8" s="33">
+      <c r="I8" s="32">
         <v>38</v>
       </c>
-      <c r="J8" s="33">
+      <c r="J8" s="32">
         <v>2.5</v>
       </c>
-      <c r="K8" s="33">
+      <c r="K8" s="32">
         <v>3.5</v>
       </c>
-      <c r="L8" s="33">
+      <c r="L8" s="32">
         <v>2</v>
       </c>
-      <c r="M8" s="33">
+      <c r="M8" s="32">
         <v>3.5</v>
       </c>
-      <c r="N8" s="33">
+      <c r="N8" s="32">
         <v>2</v>
       </c>
-      <c r="O8" s="33">
+      <c r="O8" s="32">
         <v>1.75</v>
       </c>
-      <c r="P8" s="33">
+      <c r="P8" s="32">
         <v>3.5</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="17">
         <v>65</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <v>80</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="33"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="32"/>
+      <c r="O9" s="32"/>
+      <c r="P9" s="32"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="17">
         <v>75</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <v>90</v>
       </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="17">
         <v>85</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="17">
         <v>100</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="32"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="47" t="s">
+      <c r="B12" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="17">
         <v>95</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="17">
         <v>110</v>
       </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="32"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="C13" s="43">
+      <c r="C13" s="42">
         <v>12</v>
       </c>
-      <c r="D13" s="43">
+      <c r="D13" s="42">
         <v>13</v>
       </c>
-      <c r="E13" s="44"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="45"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="45"/>
-      <c r="O13" s="45"/>
-      <c r="P13" s="45"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="45"/>
+      <c r="N13" s="44"/>
+      <c r="O13" s="44"/>
+      <c r="P13" s="44"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="43">
+      <c r="C14" s="42">
         <v>22</v>
       </c>
-      <c r="D14" s="43">
+      <c r="D14" s="42">
         <v>22</v>
       </c>
-      <c r="E14" s="44"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="45"/>
-      <c r="L14" s="45"/>
-      <c r="M14" s="46"/>
-      <c r="N14" s="45"/>
-      <c r="O14" s="45"/>
-      <c r="P14" s="45"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="45"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="44"/>
+      <c r="P14" s="44"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="42" t="s">
+      <c r="A15" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="42">
         <v>25</v>
       </c>
-      <c r="D15" s="43">
+      <c r="D15" s="42">
         <v>28</v>
       </c>
-      <c r="E15" s="44"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="45"/>
-      <c r="M15" s="46"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="45"/>
-      <c r="P15" s="45"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="45"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="44"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="42">
         <v>30</v>
       </c>
-      <c r="D16" s="43">
+      <c r="D16" s="42">
         <v>33</v>
       </c>
-      <c r="E16" s="44"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="45"/>
-      <c r="M16" s="46"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="45"/>
-      <c r="P16" s="45"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="44"/>
+      <c r="M16" s="45"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="44"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="42" t="s">
+      <c r="A17" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="42">
         <v>35</v>
       </c>
-      <c r="D17" s="43">
+      <c r="D17" s="42">
         <v>38</v>
       </c>
-      <c r="E17" s="44"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="45"/>
-      <c r="M17" s="46"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="45"/>
-      <c r="P17" s="45"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="44"/>
+      <c r="L17" s="44"/>
+      <c r="M17" s="45"/>
+      <c r="N17" s="44"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="44"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="C18" s="43">
+      <c r="C18" s="42">
         <v>45</v>
       </c>
-      <c r="D18" s="43">
+      <c r="D18" s="42">
         <v>50</v>
       </c>
-      <c r="E18" s="44"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45"/>
-      <c r="M18" s="46"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="45"/>
-      <c r="P18" s="45"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="44"/>
+      <c r="L18" s="44"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="44"/>
+      <c r="O18" s="44"/>
+      <c r="P18" s="44"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="42" t="s">
+      <c r="A19" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="C19" s="43">
+      <c r="C19" s="42">
         <v>55</v>
       </c>
-      <c r="D19" s="43">
+      <c r="D19" s="42">
         <v>60</v>
       </c>
-      <c r="E19" s="44"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="45"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="45"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="45"/>
-      <c r="P19" s="45"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="44"/>
+      <c r="M19" s="45"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="44"/>
+      <c r="P19" s="44"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="42" t="s">
+      <c r="A20" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="B20" s="48" t="s">
+      <c r="B20" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="42">
         <v>65</v>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="42">
         <v>72</v>
       </c>
-      <c r="E20" s="44"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="45"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="45"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="45"/>
-      <c r="P20" s="45"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="44"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="44"/>
+      <c r="O20" s="44"/>
+      <c r="P20" s="44"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="42" t="s">
+      <c r="A21" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="B21" s="48" t="s">
+      <c r="B21" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="C21" s="43">
+      <c r="C21" s="42">
         <v>75</v>
       </c>
-      <c r="D21" s="43">
+      <c r="D21" s="42">
         <v>83</v>
       </c>
-      <c r="E21" s="44"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="45"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="45"/>
-      <c r="P21" s="45"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="45"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="44"/>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A52" s="13"/>
-      <c r="B52" s="13"/>
+      <c r="A52" s="12"/>
+      <c r="B52" s="12"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
-      <c r="F52" s="36"/>
-      <c r="G52" s="36"/>
-      <c r="H52" s="37"/>
-      <c r="I52" s="38"/>
-      <c r="J52" s="36"/>
-      <c r="K52" s="36"/>
-      <c r="L52" s="36"/>
-      <c r="M52" s="39"/>
-      <c r="N52" s="36"/>
-      <c r="O52" s="36"/>
-      <c r="P52" s="36"/>
+      <c r="F52" s="35"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="36"/>
+      <c r="I52" s="37"/>
+      <c r="J52" s="35"/>
+      <c r="K52" s="35"/>
+      <c r="L52" s="35"/>
+      <c r="M52" s="38"/>
+      <c r="N52" s="35"/>
+      <c r="O52" s="35"/>
+      <c r="P52" s="35"/>
       <c r="Q52" s="4"/>
       <c r="R52" s="4"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A53" s="15"/>
-      <c r="B53" s="15"/>
-      <c r="H53" s="40"/>
-      <c r="I53" s="41"/>
+      <c r="A53" s="14"/>
+      <c r="B53" s="14"/>
+      <c r="H53" s="39"/>
+      <c r="I53" s="40"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A54" s="15"/>
-      <c r="B54" s="15"/>
-      <c r="H54" s="40"/>
-      <c r="I54" s="41"/>
+      <c r="A54" s="14"/>
+      <c r="B54" s="14"/>
+      <c r="H54" s="39"/>
+      <c r="I54" s="40"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A55" s="15"/>
-      <c r="B55" s="15"/>
-      <c r="H55" s="40"/>
-      <c r="I55" s="41"/>
+      <c r="A55" s="14"/>
+      <c r="B55" s="14"/>
+      <c r="H55" s="39"/>
+      <c r="I55" s="40"/>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A56" s="15"/>
-      <c r="B56" s="15"/>
-      <c r="H56" s="40"/>
-      <c r="I56" s="41"/>
+      <c r="A56" s="14"/>
+      <c r="B56" s="14"/>
+      <c r="H56" s="39"/>
+      <c r="I56" s="40"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A57" s="15"/>
-      <c r="B57" s="15"/>
-      <c r="H57" s="40"/>
-      <c r="I57" s="41"/>
-    </row>
-    <row r="58" spans="1:18" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="15"/>
-      <c r="B58" s="15"/>
+      <c r="A57" s="14"/>
+      <c r="B57" s="14"/>
+      <c r="H57" s="39"/>
+      <c r="I57" s="40"/>
+    </row>
+    <row r="58" spans="1:18" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="14"/>
+      <c r="B58" s="14"/>
       <c r="C58"/>
       <c r="D58"/>
       <c r="E58"/>
-      <c r="F58" s="34"/>
-      <c r="G58" s="34"/>
-      <c r="H58" s="40"/>
-      <c r="I58" s="41"/>
-      <c r="J58" s="34"/>
-      <c r="K58" s="34"/>
-      <c r="L58" s="34"/>
-      <c r="M58" s="35"/>
-      <c r="N58" s="34"/>
-      <c r="O58" s="34"/>
-      <c r="P58" s="34"/>
+      <c r="F58" s="33"/>
+      <c r="G58" s="33"/>
+      <c r="H58" s="39"/>
+      <c r="I58" s="40"/>
+      <c r="J58" s="33"/>
+      <c r="K58" s="33"/>
+      <c r="L58" s="33"/>
+      <c r="M58" s="34"/>
+      <c r="N58" s="33"/>
+      <c r="O58" s="33"/>
+      <c r="P58" s="33"/>
       <c r="Q58"/>
       <c r="R58"/>
     </row>
-    <row r="59" spans="1:18" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="15"/>
-      <c r="B59" s="15"/>
+    <row r="59" spans="1:18" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="14"/>
+      <c r="B59" s="14"/>
       <c r="C59"/>
       <c r="D59"/>
       <c r="E59"/>
-      <c r="F59" s="34"/>
-      <c r="G59" s="34"/>
-      <c r="H59" s="40"/>
-      <c r="I59" s="41"/>
-      <c r="J59" s="34"/>
-      <c r="K59" s="34"/>
-      <c r="L59" s="34"/>
-      <c r="M59" s="35"/>
-      <c r="N59" s="34"/>
-      <c r="O59" s="34"/>
-      <c r="P59" s="34"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="33"/>
+      <c r="H59" s="39"/>
+      <c r="I59" s="40"/>
+      <c r="J59" s="33"/>
+      <c r="K59" s="33"/>
+      <c r="L59" s="33"/>
+      <c r="M59" s="34"/>
+      <c r="N59" s="33"/>
+      <c r="O59" s="33"/>
+      <c r="P59" s="33"/>
       <c r="Q59"/>
       <c r="R59"/>
     </row>
-    <row r="60" spans="1:18" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="15"/>
-      <c r="B60" s="15"/>
+    <row r="60" spans="1:18" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="14"/>
+      <c r="B60" s="14"/>
       <c r="C60"/>
       <c r="D60"/>
       <c r="E60"/>
-      <c r="F60" s="34"/>
-      <c r="G60" s="34"/>
-      <c r="H60" s="40"/>
-      <c r="I60" s="41"/>
-      <c r="J60" s="34"/>
-      <c r="K60" s="34"/>
-      <c r="L60" s="34"/>
-      <c r="M60" s="35"/>
-      <c r="N60" s="34"/>
-      <c r="O60" s="34"/>
-      <c r="P60" s="34"/>
+      <c r="F60" s="33"/>
+      <c r="G60" s="33"/>
+      <c r="H60" s="39"/>
+      <c r="I60" s="40"/>
+      <c r="J60" s="33"/>
+      <c r="K60" s="33"/>
+      <c r="L60" s="33"/>
+      <c r="M60" s="34"/>
+      <c r="N60" s="33"/>
+      <c r="O60" s="33"/>
+      <c r="P60" s="33"/>
       <c r="Q60"/>
       <c r="R60"/>
     </row>
-    <row r="61" spans="1:18" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="15"/>
-      <c r="B61" s="15"/>
+    <row r="61" spans="1:18" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="14"/>
+      <c r="B61" s="14"/>
       <c r="C61"/>
       <c r="D61"/>
       <c r="E61"/>
-      <c r="F61" s="34"/>
-      <c r="G61" s="34"/>
-      <c r="H61" s="40"/>
-      <c r="I61" s="41"/>
-      <c r="J61" s="34"/>
-      <c r="K61" s="34"/>
-      <c r="L61" s="34"/>
-      <c r="M61" s="35"/>
-      <c r="N61" s="34"/>
-      <c r="O61" s="34"/>
-      <c r="P61" s="34"/>
+      <c r="F61" s="33"/>
+      <c r="G61" s="33"/>
+      <c r="H61" s="39"/>
+      <c r="I61" s="40"/>
+      <c r="J61" s="33"/>
+      <c r="K61" s="33"/>
+      <c r="L61" s="33"/>
+      <c r="M61" s="34"/>
+      <c r="N61" s="33"/>
+      <c r="O61" s="33"/>
+      <c r="P61" s="33"/>
       <c r="Q61"/>
       <c r="R61"/>
     </row>
-    <row r="62" spans="1:18" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="15"/>
-      <c r="B62" s="15"/>
+    <row r="62" spans="1:18" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="14"/>
+      <c r="B62" s="14"/>
       <c r="C62"/>
       <c r="D62"/>
       <c r="E62"/>
-      <c r="F62" s="34"/>
-      <c r="G62" s="34"/>
-      <c r="H62" s="40"/>
-      <c r="I62" s="41"/>
-      <c r="J62" s="34"/>
-      <c r="K62" s="34"/>
-      <c r="L62" s="34"/>
-      <c r="M62" s="35"/>
-      <c r="N62" s="34"/>
-      <c r="O62" s="34"/>
-      <c r="P62" s="34"/>
+      <c r="F62" s="33"/>
+      <c r="G62" s="33"/>
+      <c r="H62" s="39"/>
+      <c r="I62" s="40"/>
+      <c r="J62" s="33"/>
+      <c r="K62" s="33"/>
+      <c r="L62" s="33"/>
+      <c r="M62" s="34"/>
+      <c r="N62" s="33"/>
+      <c r="O62" s="33"/>
+      <c r="P62" s="33"/>
       <c r="Q62"/>
       <c r="R62"/>
     </row>
-    <row r="63" spans="1:18" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="15"/>
-      <c r="B63" s="15"/>
+    <row r="63" spans="1:18" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="14"/>
+      <c r="B63" s="14"/>
       <c r="C63"/>
       <c r="D63"/>
       <c r="E63"/>
-      <c r="F63" s="34"/>
-      <c r="G63" s="34"/>
-      <c r="H63" s="40"/>
-      <c r="I63" s="41"/>
-      <c r="J63" s="34"/>
-      <c r="K63" s="34"/>
-      <c r="L63" s="34"/>
-      <c r="M63" s="35"/>
-      <c r="N63" s="34"/>
-      <c r="O63" s="34"/>
-      <c r="P63" s="34"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="33"/>
+      <c r="H63" s="39"/>
+      <c r="I63" s="40"/>
+      <c r="J63" s="33"/>
+      <c r="K63" s="33"/>
+      <c r="L63" s="33"/>
+      <c r="M63" s="34"/>
+      <c r="N63" s="33"/>
+      <c r="O63" s="33"/>
+      <c r="P63" s="33"/>
       <c r="Q63"/>
       <c r="R63"/>
     </row>
-    <row r="64" spans="1:18" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="15"/>
-      <c r="B64" s="15"/>
+    <row r="64" spans="1:18" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="14"/>
+      <c r="B64" s="14"/>
       <c r="C64"/>
       <c r="D64"/>
       <c r="E64"/>
-      <c r="F64" s="34"/>
-      <c r="G64" s="34"/>
-      <c r="H64" s="40"/>
-      <c r="I64" s="41"/>
-      <c r="J64" s="34"/>
-      <c r="K64" s="34"/>
-      <c r="L64" s="34"/>
-      <c r="M64" s="35"/>
-      <c r="N64" s="34"/>
-      <c r="O64" s="34"/>
-      <c r="P64" s="34"/>
+      <c r="F64" s="33"/>
+      <c r="G64" s="33"/>
+      <c r="H64" s="39"/>
+      <c r="I64" s="40"/>
+      <c r="J64" s="33"/>
+      <c r="K64" s="33"/>
+      <c r="L64" s="33"/>
+      <c r="M64" s="34"/>
+      <c r="N64" s="33"/>
+      <c r="O64" s="33"/>
+      <c r="P64" s="33"/>
       <c r="Q64"/>
       <c r="R64"/>
     </row>
-    <row r="65" spans="1:18" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="15"/>
-      <c r="B65" s="15"/>
+    <row r="65" spans="1:18" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="14"/>
+      <c r="B65" s="14"/>
       <c r="C65"/>
       <c r="D65"/>
       <c r="E65"/>
-      <c r="F65" s="34"/>
-      <c r="G65" s="34"/>
-      <c r="H65" s="40"/>
-      <c r="I65" s="41"/>
-      <c r="J65" s="34"/>
-      <c r="K65" s="34"/>
-      <c r="L65" s="34"/>
-      <c r="M65" s="35"/>
-      <c r="N65" s="34"/>
-      <c r="O65" s="34"/>
-      <c r="P65" s="34"/>
+      <c r="F65" s="33"/>
+      <c r="G65" s="33"/>
+      <c r="H65" s="39"/>
+      <c r="I65" s="40"/>
+      <c r="J65" s="33"/>
+      <c r="K65" s="33"/>
+      <c r="L65" s="33"/>
+      <c r="M65" s="34"/>
+      <c r="N65" s="33"/>
+      <c r="O65" s="33"/>
+      <c r="P65" s="33"/>
       <c r="Q65"/>
       <c r="R65"/>
     </row>
-    <row r="66" spans="1:18" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="15"/>
-      <c r="B66" s="15"/>
+    <row r="66" spans="1:18" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="14"/>
+      <c r="B66" s="14"/>
       <c r="C66"/>
       <c r="D66"/>
       <c r="E66"/>
-      <c r="F66" s="34"/>
-      <c r="G66" s="34"/>
-      <c r="H66" s="40"/>
-      <c r="I66" s="41"/>
-      <c r="J66" s="34"/>
-      <c r="K66" s="34"/>
-      <c r="L66" s="34"/>
-      <c r="M66" s="35"/>
-      <c r="N66" s="34"/>
-      <c r="O66" s="34"/>
-      <c r="P66" s="34"/>
+      <c r="F66" s="33"/>
+      <c r="G66" s="33"/>
+      <c r="H66" s="39"/>
+      <c r="I66" s="40"/>
+      <c r="J66" s="33"/>
+      <c r="K66" s="33"/>
+      <c r="L66" s="33"/>
+      <c r="M66" s="34"/>
+      <c r="N66" s="33"/>
+      <c r="O66" s="33"/>
+      <c r="P66" s="33"/>
       <c r="Q66"/>
       <c r="R66"/>
     </row>
-    <row r="67" spans="1:18" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="15"/>
-      <c r="B67" s="15"/>
+    <row r="67" spans="1:18" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="14"/>
+      <c r="B67" s="14"/>
       <c r="C67"/>
       <c r="D67"/>
       <c r="E67"/>
-      <c r="F67" s="34"/>
-      <c r="G67" s="34"/>
-      <c r="H67" s="40"/>
-      <c r="I67" s="41"/>
-      <c r="J67" s="34"/>
-      <c r="K67" s="34"/>
-      <c r="L67" s="34"/>
-      <c r="M67" s="35"/>
-      <c r="N67" s="34"/>
-      <c r="O67" s="34"/>
-      <c r="P67" s="34"/>
+      <c r="F67" s="33"/>
+      <c r="G67" s="33"/>
+      <c r="H67" s="39"/>
+      <c r="I67" s="40"/>
+      <c r="J67" s="33"/>
+      <c r="K67" s="33"/>
+      <c r="L67" s="33"/>
+      <c r="M67" s="34"/>
+      <c r="N67" s="33"/>
+      <c r="O67" s="33"/>
+      <c r="P67" s="33"/>
       <c r="Q67"/>
       <c r="R67"/>
     </row>
-    <row r="68" spans="1:18" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="15"/>
-      <c r="B68" s="15"/>
+    <row r="68" spans="1:18" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="14"/>
+      <c r="B68" s="14"/>
       <c r="C68"/>
       <c r="D68"/>
       <c r="E68"/>
-      <c r="F68" s="34"/>
-      <c r="G68" s="34"/>
-      <c r="H68" s="40"/>
-      <c r="I68" s="41"/>
-      <c r="J68" s="34"/>
-      <c r="K68" s="34"/>
-      <c r="L68" s="34"/>
-      <c r="M68" s="35"/>
-      <c r="N68" s="34"/>
-      <c r="O68" s="34"/>
-      <c r="P68" s="34"/>
+      <c r="F68" s="33"/>
+      <c r="G68" s="33"/>
+      <c r="H68" s="39"/>
+      <c r="I68" s="40"/>
+      <c r="J68" s="33"/>
+      <c r="K68" s="33"/>
+      <c r="L68" s="33"/>
+      <c r="M68" s="34"/>
+      <c r="N68" s="33"/>
+      <c r="O68" s="33"/>
+      <c r="P68" s="33"/>
       <c r="Q68"/>
       <c r="R68"/>
     </row>
-    <row r="69" spans="1:18" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="15"/>
-      <c r="B69" s="15"/>
+    <row r="69" spans="1:18" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="14"/>
+      <c r="B69" s="14"/>
       <c r="C69"/>
       <c r="D69"/>
       <c r="E69"/>
-      <c r="F69" s="34"/>
-      <c r="G69" s="34"/>
-      <c r="H69" s="40"/>
-      <c r="I69" s="41"/>
-      <c r="J69" s="34"/>
-      <c r="K69" s="34"/>
-      <c r="L69" s="34"/>
-      <c r="M69" s="35"/>
-      <c r="N69" s="34"/>
-      <c r="O69" s="34"/>
-      <c r="P69" s="34"/>
+      <c r="F69" s="33"/>
+      <c r="G69" s="33"/>
+      <c r="H69" s="39"/>
+      <c r="I69" s="40"/>
+      <c r="J69" s="33"/>
+      <c r="K69" s="33"/>
+      <c r="L69" s="33"/>
+      <c r="M69" s="34"/>
+      <c r="N69" s="33"/>
+      <c r="O69" s="33"/>
+      <c r="P69" s="33"/>
       <c r="Q69"/>
       <c r="R69"/>
     </row>
@@ -2237,1062 +2239,1062 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="15.140625" customWidth="1"/>
     <col min="3" max="6" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="29"/>
+    <col min="7" max="7" width="11.42578125" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="H1" s="49" t="s">
+      <c r="H1" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="I1" s="49" t="s">
+      <c r="I1" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="J1" s="49" t="s">
+      <c r="J1" s="10" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="C2" s="18">
+      <c r="C2" s="17">
         <v>235</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="17">
         <v>360</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="17">
         <v>215</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="17">
         <v>360</v>
       </c>
-      <c r="G2" s="64">
+      <c r="G2" s="61">
         <v>210000</v>
       </c>
-      <c r="H2" s="65">
+      <c r="H2" s="15">
         <v>0.3</v>
       </c>
-      <c r="I2" s="66">
+      <c r="I2" s="62">
         <f>G2/(2*(1+H2))</f>
         <v>80769.230769230766</v>
       </c>
-      <c r="J2" s="67">
+      <c r="J2" s="63">
         <v>1.2E-5</v>
       </c>
-      <c r="K2" s="63"/>
+      <c r="K2" s="60"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="17">
         <v>275</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="17">
         <v>430</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="17">
         <v>255</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="17">
         <v>410</v>
       </c>
-      <c r="G3" s="64">
+      <c r="G3" s="61">
         <v>210000</v>
       </c>
-      <c r="H3" s="65">
+      <c r="H3" s="15">
         <v>0.3</v>
       </c>
-      <c r="I3" s="66">
+      <c r="I3" s="62">
         <f t="shared" ref="I3:I33" si="0">G3/(2*(1+H3))</f>
         <v>80769.230769230766</v>
       </c>
-      <c r="J3" s="67">
+      <c r="J3" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="17">
         <v>355</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="17">
         <v>490</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="17">
         <v>335</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="17">
         <v>470</v>
       </c>
-      <c r="G4" s="64">
+      <c r="G4" s="61">
         <v>210000</v>
       </c>
-      <c r="H4" s="65">
+      <c r="H4" s="15">
         <v>0.3</v>
       </c>
-      <c r="I4" s="66">
+      <c r="I4" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J4" s="67">
+      <c r="J4" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="17">
         <v>440</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="17">
         <v>550</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="17">
         <v>410</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="17">
         <v>550</v>
       </c>
-      <c r="G5" s="64">
+      <c r="G5" s="61">
         <v>210000</v>
       </c>
-      <c r="H5" s="65">
+      <c r="H5" s="15">
         <v>0.3</v>
       </c>
-      <c r="I5" s="66">
+      <c r="I5" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J5" s="67">
+      <c r="J5" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="20">
         <v>275</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="20">
         <v>390</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="20">
         <v>255</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="20">
         <v>370</v>
       </c>
-      <c r="G6" s="64">
+      <c r="G6" s="61">
         <v>210000</v>
       </c>
-      <c r="H6" s="65">
+      <c r="H6" s="15">
         <v>0.3</v>
       </c>
-      <c r="I6" s="66">
+      <c r="I6" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J6" s="67">
+      <c r="J6" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="20">
         <v>355</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="20">
         <v>490</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="20">
         <v>335</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="20">
         <v>470</v>
       </c>
-      <c r="G7" s="64">
+      <c r="G7" s="61">
         <v>210000</v>
       </c>
-      <c r="H7" s="65">
+      <c r="H7" s="15">
         <v>0.3</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J7" s="67">
+      <c r="J7" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="20">
         <v>420</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="20">
         <v>520</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="20">
         <v>390</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="20">
         <v>520</v>
       </c>
-      <c r="G8" s="64">
+      <c r="G8" s="61">
         <v>210000</v>
       </c>
-      <c r="H8" s="65">
+      <c r="H8" s="15">
         <v>0.3</v>
       </c>
-      <c r="I8" s="66">
+      <c r="I8" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J8" s="67">
+      <c r="J8" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="20">
         <v>460</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="20">
         <v>540</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="20">
         <v>430</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="20">
         <v>540</v>
       </c>
-      <c r="G9" s="64">
+      <c r="G9" s="61">
         <v>210000</v>
       </c>
-      <c r="H9" s="65">
+      <c r="H9" s="15">
         <v>0.3</v>
       </c>
-      <c r="I9" s="66">
+      <c r="I9" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J9" s="67">
+      <c r="J9" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="C10" s="50">
+      <c r="C10" s="48">
         <v>275</v>
       </c>
-      <c r="D10" s="50">
+      <c r="D10" s="48">
         <v>370</v>
       </c>
-      <c r="E10" s="50">
+      <c r="E10" s="48">
         <v>255</v>
       </c>
-      <c r="F10" s="50">
+      <c r="F10" s="48">
         <v>360</v>
       </c>
-      <c r="G10" s="64">
+      <c r="G10" s="61">
         <v>210000</v>
       </c>
-      <c r="H10" s="65">
+      <c r="H10" s="15">
         <v>0.3</v>
       </c>
-      <c r="I10" s="66">
+      <c r="I10" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J10" s="67">
+      <c r="J10" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="C11" s="50">
+      <c r="C11" s="48">
         <v>355</v>
       </c>
-      <c r="D11" s="50">
+      <c r="D11" s="48">
         <v>470</v>
       </c>
-      <c r="E11" s="50">
+      <c r="E11" s="48">
         <v>335</v>
       </c>
-      <c r="F11" s="50">
+      <c r="F11" s="48">
         <v>450</v>
       </c>
-      <c r="G11" s="64">
+      <c r="G11" s="61">
         <v>210000</v>
       </c>
-      <c r="H11" s="65">
+      <c r="H11" s="15">
         <v>0.3</v>
       </c>
-      <c r="I11" s="66">
+      <c r="I11" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J11" s="67">
+      <c r="J11" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="C12" s="50">
+      <c r="C12" s="48">
         <v>420</v>
       </c>
-      <c r="D12" s="50">
+      <c r="D12" s="48">
         <v>520</v>
       </c>
-      <c r="E12" s="50">
+      <c r="E12" s="48">
         <v>390</v>
       </c>
-      <c r="F12" s="50">
+      <c r="F12" s="48">
         <v>500</v>
       </c>
-      <c r="G12" s="64">
+      <c r="G12" s="61">
         <v>210000</v>
       </c>
-      <c r="H12" s="65">
+      <c r="H12" s="15">
         <v>0.3</v>
       </c>
-      <c r="I12" s="66">
+      <c r="I12" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J12" s="67">
+      <c r="J12" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="50">
+      <c r="C13" s="48">
         <v>460</v>
       </c>
-      <c r="D13" s="50">
+      <c r="D13" s="48">
         <v>540</v>
       </c>
-      <c r="E13" s="50">
+      <c r="E13" s="48">
         <v>430</v>
       </c>
-      <c r="F13" s="50">
+      <c r="F13" s="48">
         <v>530</v>
       </c>
-      <c r="G13" s="64">
+      <c r="G13" s="61">
         <v>210000</v>
       </c>
-      <c r="H13" s="65">
+      <c r="H13" s="15">
         <v>0.3</v>
       </c>
-      <c r="I13" s="66">
+      <c r="I13" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J13" s="67">
+      <c r="J13" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="49" t="s">
         <v>141</v>
       </c>
-      <c r="B14" s="52" t="s">
+      <c r="B14" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="C14" s="53">
+      <c r="C14" s="51">
         <v>235</v>
       </c>
-      <c r="D14" s="53">
+      <c r="D14" s="51">
         <v>360</v>
       </c>
-      <c r="E14" s="53">
+      <c r="E14" s="51">
         <v>215</v>
       </c>
-      <c r="F14" s="53">
+      <c r="F14" s="51">
         <v>340</v>
       </c>
-      <c r="G14" s="64">
+      <c r="G14" s="61">
         <v>210000</v>
       </c>
-      <c r="H14" s="65">
+      <c r="H14" s="15">
         <v>0.3</v>
       </c>
-      <c r="I14" s="66">
+      <c r="I14" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J14" s="67">
+      <c r="J14" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="49" t="s">
         <v>143</v>
       </c>
-      <c r="B15" s="52" t="s">
+      <c r="B15" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="C15" s="53">
+      <c r="C15" s="51">
         <v>355</v>
       </c>
-      <c r="D15" s="53">
+      <c r="D15" s="51">
         <v>490</v>
       </c>
-      <c r="E15" s="53">
+      <c r="E15" s="51">
         <v>335</v>
       </c>
-      <c r="F15" s="53">
+      <c r="F15" s="51">
         <v>490</v>
       </c>
-      <c r="G15" s="64">
+      <c r="G15" s="61">
         <v>210000</v>
       </c>
-      <c r="H15" s="65">
+      <c r="H15" s="15">
         <v>0.3</v>
       </c>
-      <c r="I15" s="66">
+      <c r="I15" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J15" s="67">
+      <c r="J15" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="54" t="s">
+      <c r="A16" s="52" t="s">
         <v>144</v>
       </c>
-      <c r="B16" s="55" t="s">
+      <c r="B16" s="53" t="s">
         <v>145</v>
       </c>
-      <c r="C16" s="56">
+      <c r="C16" s="54">
         <v>460</v>
       </c>
-      <c r="D16" s="56">
+      <c r="D16" s="54">
         <v>570</v>
       </c>
-      <c r="E16" s="56">
+      <c r="E16" s="54">
         <v>440</v>
       </c>
-      <c r="F16" s="56">
+      <c r="F16" s="54">
         <v>550</v>
       </c>
-      <c r="G16" s="64">
+      <c r="G16" s="61">
         <v>210000</v>
       </c>
-      <c r="H16" s="65">
+      <c r="H16" s="15">
         <v>0.3</v>
       </c>
-      <c r="I16" s="66">
+      <c r="I16" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J16" s="67">
+      <c r="J16" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="57" t="s">
+      <c r="A17" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="B17" s="57" t="s">
+      <c r="B17" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="C17" s="58">
+      <c r="C17" s="56">
         <v>235</v>
       </c>
-      <c r="D17" s="58">
+      <c r="D17" s="56">
         <v>360</v>
       </c>
-      <c r="E17" s="58">
+      <c r="E17" s="56">
         <v>215</v>
       </c>
-      <c r="F17" s="58">
+      <c r="F17" s="56">
         <v>340</v>
       </c>
-      <c r="G17" s="64">
+      <c r="G17" s="61">
         <v>210000</v>
       </c>
-      <c r="H17" s="65">
+      <c r="H17" s="15">
         <v>0.3</v>
       </c>
-      <c r="I17" s="66">
+      <c r="I17" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J17" s="67">
+      <c r="J17" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="57" t="s">
+      <c r="A18" s="55" t="s">
         <v>148</v>
       </c>
-      <c r="B18" s="57" t="s">
+      <c r="B18" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="C18" s="58">
+      <c r="C18" s="56">
         <v>275</v>
       </c>
-      <c r="D18" s="58">
+      <c r="D18" s="56">
         <v>430</v>
       </c>
-      <c r="E18" s="58">
+      <c r="E18" s="56">
         <v>255</v>
       </c>
-      <c r="F18" s="58">
+      <c r="F18" s="56">
         <v>410</v>
       </c>
-      <c r="G18" s="64">
+      <c r="G18" s="61">
         <v>210000</v>
       </c>
-      <c r="H18" s="65">
+      <c r="H18" s="15">
         <v>0.3</v>
       </c>
-      <c r="I18" s="66">
+      <c r="I18" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J18" s="67">
+      <c r="J18" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="55" t="s">
         <v>149</v>
       </c>
-      <c r="B19" s="57" t="s">
+      <c r="B19" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="C19" s="58">
+      <c r="C19" s="56">
         <v>355</v>
       </c>
-      <c r="D19" s="58">
+      <c r="D19" s="56">
         <v>510</v>
       </c>
-      <c r="E19" s="58">
+      <c r="E19" s="56">
         <v>335</v>
       </c>
-      <c r="F19" s="58">
+      <c r="F19" s="56">
         <v>490</v>
       </c>
-      <c r="G19" s="64">
+      <c r="G19" s="61">
         <v>210000</v>
       </c>
-      <c r="H19" s="65">
+      <c r="H19" s="15">
         <v>0.3</v>
       </c>
-      <c r="I19" s="66">
+      <c r="I19" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J19" s="67">
+      <c r="J19" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="B20" s="57" t="s">
+      <c r="B20" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="C20" s="58">
+      <c r="C20" s="56">
         <v>275</v>
       </c>
-      <c r="D20" s="58">
+      <c r="D20" s="56">
         <v>390</v>
       </c>
-      <c r="E20" s="58">
+      <c r="E20" s="56">
         <v>255</v>
       </c>
-      <c r="F20" s="58">
+      <c r="F20" s="56">
         <v>370</v>
       </c>
-      <c r="G20" s="64">
+      <c r="G20" s="61">
         <v>210000</v>
       </c>
-      <c r="H20" s="65">
+      <c r="H20" s="15">
         <v>0.3</v>
       </c>
-      <c r="I20" s="66">
+      <c r="I20" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J20" s="67">
+      <c r="J20" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="57" t="s">
+      <c r="A21" s="55" t="s">
         <v>151</v>
       </c>
-      <c r="B21" s="57" t="s">
+      <c r="B21" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="C21" s="58">
+      <c r="C21" s="56">
         <v>355</v>
       </c>
-      <c r="D21" s="58">
+      <c r="D21" s="56">
         <v>490</v>
       </c>
-      <c r="E21" s="58">
+      <c r="E21" s="56">
         <v>335</v>
       </c>
-      <c r="F21" s="58">
+      <c r="F21" s="56">
         <v>470</v>
       </c>
-      <c r="G21" s="64">
+      <c r="G21" s="61">
         <v>210000</v>
       </c>
-      <c r="H21" s="65">
+      <c r="H21" s="15">
         <v>0.3</v>
       </c>
-      <c r="I21" s="66">
+      <c r="I21" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J21" s="67">
+      <c r="J21" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="57" t="s">
+      <c r="A22" s="55" t="s">
         <v>152</v>
       </c>
-      <c r="B22" s="57" t="s">
+      <c r="B22" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="C22" s="58">
+      <c r="C22" s="56">
         <v>420</v>
       </c>
-      <c r="D22" s="58">
+      <c r="D22" s="56">
         <v>540</v>
       </c>
-      <c r="E22" s="58">
+      <c r="E22" s="56">
         <v>390</v>
       </c>
-      <c r="F22" s="58">
+      <c r="F22" s="56">
         <v>520</v>
       </c>
-      <c r="G22" s="64">
+      <c r="G22" s="61">
         <v>210000</v>
       </c>
-      <c r="H22" s="65">
+      <c r="H22" s="15">
         <v>0.3</v>
       </c>
-      <c r="I22" s="66">
+      <c r="I22" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J22" s="67">
+      <c r="J22" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="57" t="s">
+      <c r="A23" s="55" t="s">
         <v>153</v>
       </c>
-      <c r="B23" s="57" t="s">
+      <c r="B23" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="C23" s="58">
+      <c r="C23" s="56">
         <v>460</v>
       </c>
-      <c r="D23" s="58">
+      <c r="D23" s="56">
         <v>560</v>
       </c>
-      <c r="E23" s="58">
+      <c r="E23" s="56">
         <v>430</v>
       </c>
-      <c r="F23" s="58">
+      <c r="F23" s="56">
         <v>550</v>
       </c>
-      <c r="G23" s="64">
+      <c r="G23" s="61">
         <v>210000</v>
       </c>
-      <c r="H23" s="65">
+      <c r="H23" s="15">
         <v>0.3</v>
       </c>
-      <c r="I23" s="66">
+      <c r="I23" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J23" s="67">
+      <c r="J23" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="59" t="s">
+      <c r="A24" s="57" t="s">
         <v>146</v>
       </c>
-      <c r="B24" s="59" t="s">
+      <c r="B24" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="C24" s="60">
+      <c r="C24" s="58">
         <v>235</v>
       </c>
-      <c r="D24" s="60">
+      <c r="D24" s="58">
         <v>360</v>
       </c>
-      <c r="E24" s="61"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="64">
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="61">
         <v>210000</v>
       </c>
-      <c r="H24" s="65">
+      <c r="H24" s="15">
         <v>0.3</v>
       </c>
-      <c r="I24" s="66">
+      <c r="I24" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J24" s="67">
+      <c r="J24" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="59" t="s">
+      <c r="A25" s="57" t="s">
         <v>148</v>
       </c>
-      <c r="B25" s="59" t="s">
+      <c r="B25" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="C25" s="60">
+      <c r="C25" s="58">
         <v>275</v>
       </c>
-      <c r="D25" s="60">
+      <c r="D25" s="58">
         <v>430</v>
       </c>
-      <c r="E25" s="61"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="64">
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="61">
         <v>210000</v>
       </c>
-      <c r="H25" s="65">
+      <c r="H25" s="15">
         <v>0.3</v>
       </c>
-      <c r="I25" s="66">
+      <c r="I25" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J25" s="67">
+      <c r="J25" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="59" t="s">
+      <c r="A26" s="57" t="s">
         <v>149</v>
       </c>
-      <c r="B26" s="59" t="s">
+      <c r="B26" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="C26" s="60">
+      <c r="C26" s="58">
         <v>355</v>
       </c>
-      <c r="D26" s="60">
+      <c r="D26" s="58">
         <v>510</v>
       </c>
-      <c r="E26" s="61"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="64">
+      <c r="E26" s="59"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="61">
         <v>210000</v>
       </c>
-      <c r="H26" s="65">
+      <c r="H26" s="15">
         <v>0.3</v>
       </c>
-      <c r="I26" s="66">
+      <c r="I26" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J26" s="67">
+      <c r="J26" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="59" t="s">
+      <c r="A27" s="57" t="s">
         <v>150</v>
       </c>
-      <c r="B27" s="59" t="s">
+      <c r="B27" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="C27" s="60">
+      <c r="C27" s="58">
         <v>275</v>
       </c>
-      <c r="D27" s="60">
+      <c r="D27" s="58">
         <v>370</v>
       </c>
-      <c r="E27" s="61"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="64">
+      <c r="E27" s="59"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="61">
         <v>210000</v>
       </c>
-      <c r="H27" s="65">
+      <c r="H27" s="15">
         <v>0.3</v>
       </c>
-      <c r="I27" s="66">
+      <c r="I27" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J27" s="67">
+      <c r="J27" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="59" t="s">
+      <c r="A28" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="B28" s="59" t="s">
+      <c r="B28" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="C28" s="60">
+      <c r="C28" s="58">
         <v>355</v>
       </c>
-      <c r="D28" s="60">
+      <c r="D28" s="58">
         <v>470</v>
       </c>
-      <c r="E28" s="61"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="64">
+      <c r="E28" s="59"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="61">
         <v>210000</v>
       </c>
-      <c r="H28" s="65">
+      <c r="H28" s="15">
         <v>0.3</v>
       </c>
-      <c r="I28" s="66">
+      <c r="I28" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J28" s="67">
+      <c r="J28" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="59" t="s">
+      <c r="A29" s="57" t="s">
         <v>153</v>
       </c>
-      <c r="B29" s="59" t="s">
+      <c r="B29" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="C29" s="60">
+      <c r="C29" s="58">
         <v>460</v>
       </c>
-      <c r="D29" s="60">
+      <c r="D29" s="58">
         <v>550</v>
       </c>
-      <c r="E29" s="61"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="64">
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="61">
         <v>210000</v>
       </c>
-      <c r="H29" s="65">
+      <c r="H29" s="15">
         <v>0.3</v>
       </c>
-      <c r="I29" s="66">
+      <c r="I29" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J29" s="67">
+      <c r="J29" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="59" t="s">
+      <c r="A30" s="57" t="s">
         <v>155</v>
       </c>
-      <c r="B30" s="59" t="s">
+      <c r="B30" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="C30" s="60">
+      <c r="C30" s="58">
         <v>275</v>
       </c>
-      <c r="D30" s="60">
+      <c r="D30" s="58">
         <v>360</v>
       </c>
-      <c r="E30" s="61"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="64">
+      <c r="E30" s="59"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="61">
         <v>210000</v>
       </c>
-      <c r="H30" s="65">
+      <c r="H30" s="15">
         <v>0.3</v>
       </c>
-      <c r="I30" s="66">
+      <c r="I30" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J30" s="67">
+      <c r="J30" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="59" t="s">
+      <c r="A31" s="57" t="s">
         <v>156</v>
       </c>
-      <c r="B31" s="59" t="s">
+      <c r="B31" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="C31" s="60">
+      <c r="C31" s="58">
         <v>355</v>
       </c>
-      <c r="D31" s="60">
+      <c r="D31" s="58">
         <v>470</v>
       </c>
-      <c r="E31" s="61"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="64">
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="61">
         <v>210000</v>
       </c>
-      <c r="H31" s="65">
+      <c r="H31" s="15">
         <v>0.3</v>
       </c>
-      <c r="I31" s="66">
+      <c r="I31" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J31" s="67">
+      <c r="J31" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="59" t="s">
+      <c r="A32" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="B32" s="59" t="s">
+      <c r="B32" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="C32" s="60">
+      <c r="C32" s="58">
         <v>420</v>
       </c>
-      <c r="D32" s="60">
+      <c r="D32" s="58">
         <v>500</v>
       </c>
-      <c r="E32" s="61"/>
-      <c r="F32" s="62"/>
-      <c r="G32" s="64">
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="61">
         <v>210000</v>
       </c>
-      <c r="H32" s="65">
+      <c r="H32" s="15">
         <v>0.3</v>
       </c>
-      <c r="I32" s="66">
+      <c r="I32" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J32" s="67">
+      <c r="J32" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="59" t="s">
+      <c r="A33" s="57" t="s">
         <v>158</v>
       </c>
-      <c r="B33" s="59" t="s">
+      <c r="B33" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="C33" s="60">
+      <c r="C33" s="58">
         <v>460</v>
       </c>
-      <c r="D33" s="60">
+      <c r="D33" s="58">
         <v>530</v>
       </c>
-      <c r="E33" s="61"/>
-      <c r="F33" s="62"/>
-      <c r="G33" s="64">
+      <c r="E33" s="59"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="61">
         <v>210000</v>
       </c>
-      <c r="H33" s="65">
+      <c r="H33" s="15">
         <v>0.3</v>
       </c>
-      <c r="I33" s="66">
+      <c r="I33" s="62">
         <f t="shared" si="0"/>
         <v>80769.230769230766</v>
       </c>
-      <c r="J33" s="67">
+      <c r="J33" s="63">
         <v>1.2E-5</v>
       </c>
     </row>
@@ -3303,55 +3305,55 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:T98"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" style="13" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.42578125" style="6"/>
-    <col min="9" max="10" width="15.140625" style="29" customWidth="1"/>
+    <col min="9" max="10" width="15.140625" style="28" customWidth="1"/>
     <col min="11" max="11" width="15.140625" customWidth="1"/>
     <col min="12" max="12" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="10" t="s">
         <v>25</v>
       </c>
       <c r="N1" s="3" t="s">
@@ -3363,2314 +3365,2290 @@
       <c r="P1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="Q1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="R1" s="10" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="17">
         <v>14</v>
       </c>
-      <c r="C2" s="18">
+      <c r="C2" s="17">
         <v>7.2</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="17">
         <v>0.4</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="17">
         <v>16</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="17">
         <v>2</v>
       </c>
-      <c r="G2" s="18">
+      <c r="G2" s="17">
         <v>3</v>
       </c>
-      <c r="H2" s="18">
+      <c r="H2" s="17">
         <f>2*D2</f>
         <v>0.8</v>
       </c>
-      <c r="I2" s="26">
+      <c r="I2" s="25">
         <v>7000</v>
       </c>
-      <c r="J2" s="26">
+      <c r="J2" s="25">
         <v>4700</v>
       </c>
-      <c r="K2" s="18">
+      <c r="K2" s="17">
         <v>230</v>
       </c>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18">
+      <c r="L2" s="17"/>
+      <c r="M2" s="17">
         <v>440</v>
       </c>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18">
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17">
         <v>290</v>
       </c>
-      <c r="R2" s="18">
+      <c r="R2" s="17">
         <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="17">
         <v>16</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="17">
         <v>8.5</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="17">
         <v>0.4</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="17">
         <v>17</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="17">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="17">
         <v>3.2</v>
       </c>
-      <c r="H3" s="18">
+      <c r="H3" s="17">
         <f t="shared" ref="H3:H27" si="0">2*D3</f>
         <v>0.8</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="25">
         <v>8000</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="25">
         <v>5400</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="17">
         <v>270</v>
       </c>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18">
+      <c r="L3" s="17"/>
+      <c r="M3" s="17">
         <v>500</v>
       </c>
-      <c r="N3" s="18"/>
-      <c r="O3" s="18"/>
-      <c r="P3" s="18"/>
-      <c r="Q3" s="18">
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17">
         <v>310</v>
       </c>
-      <c r="R3" s="18">
+      <c r="R3" s="17">
         <v>370</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="17">
         <v>18</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="17">
         <v>10</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="17">
         <v>0.4</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="17">
         <v>18</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="17">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="17">
         <v>3.4</v>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="17">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="I4" s="26">
+      <c r="I4" s="25">
         <v>9000</v>
       </c>
-      <c r="J4" s="26">
+      <c r="J4" s="25">
         <v>6000</v>
       </c>
-      <c r="K4" s="18">
+      <c r="K4" s="17">
         <v>300</v>
       </c>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18">
+      <c r="L4" s="17"/>
+      <c r="M4" s="17">
         <v>560</v>
       </c>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="18">
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17">
         <v>320</v>
       </c>
-      <c r="R4" s="18">
+      <c r="R4" s="17">
         <v>380</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="17">
         <v>20</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="17">
         <v>11.5</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="17">
         <v>0.4</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="17">
         <v>19</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="17">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="17">
         <v>3.6</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="17">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="25">
         <v>9500</v>
       </c>
-      <c r="J5" s="26">
+      <c r="J5" s="25">
         <v>6400</v>
       </c>
-      <c r="K5" s="18">
+      <c r="K5" s="17">
         <v>320</v>
       </c>
-      <c r="L5" s="18"/>
-      <c r="M5" s="18">
+      <c r="L5" s="17"/>
+      <c r="M5" s="17">
         <v>590</v>
       </c>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18">
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17">
         <v>330</v>
       </c>
-      <c r="R5" s="18">
+      <c r="R5" s="17">
         <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="17">
         <v>22</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="17">
         <v>13</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="17">
         <v>0.4</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="17">
         <v>20</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="17">
         <v>2.4</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="17">
         <v>3.8</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="17">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="25">
         <v>10000</v>
       </c>
-      <c r="J6" s="26">
+      <c r="J6" s="25">
         <v>6700</v>
       </c>
-      <c r="K6" s="18">
+      <c r="K6" s="17">
         <v>330</v>
       </c>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18">
+      <c r="L6" s="17"/>
+      <c r="M6" s="17">
         <v>630</v>
       </c>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18">
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17">
         <v>340</v>
       </c>
-      <c r="R6" s="18">
+      <c r="R6" s="17">
         <v>410</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="17">
         <v>24</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="17">
         <v>14.5</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <v>0.4</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="17">
         <v>21</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="17">
         <v>2.5</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="17">
         <v>4</v>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="17">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="25">
         <v>11000</v>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="25">
         <v>7400</v>
       </c>
-      <c r="K7" s="18">
+      <c r="K7" s="17">
         <v>370</v>
       </c>
-      <c r="L7" s="18"/>
-      <c r="M7" s="18">
+      <c r="L7" s="17"/>
+      <c r="M7" s="17">
         <v>690</v>
       </c>
-      <c r="N7" s="18"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="18"/>
-      <c r="Q7" s="18">
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17">
         <v>350</v>
       </c>
-      <c r="R7" s="18">
+      <c r="R7" s="17">
         <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="17">
         <v>27</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="17">
         <v>16.5</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <v>0.4</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="17">
         <v>22</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <v>2.5</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="17">
         <v>4</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="17">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="25">
         <v>11500</v>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="25">
         <v>7700</v>
       </c>
-      <c r="K8" s="18">
+      <c r="K8" s="17">
         <v>380</v>
       </c>
-      <c r="L8" s="18"/>
-      <c r="M8" s="18">
+      <c r="L8" s="17"/>
+      <c r="M8" s="17">
         <v>720</v>
       </c>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="18">
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17">
         <v>360</v>
       </c>
-      <c r="R8" s="18">
+      <c r="R8" s="17">
         <v>430</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="17">
         <v>30</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="17">
         <v>19</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <v>0.4</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="17">
         <v>24</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="17">
         <v>2.7</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="17">
         <v>4</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="17">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="25">
         <v>12000</v>
       </c>
-      <c r="J9" s="26">
+      <c r="J9" s="25">
         <v>8000</v>
       </c>
-      <c r="K9" s="18">
+      <c r="K9" s="17">
         <v>400</v>
       </c>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18">
+      <c r="L9" s="17"/>
+      <c r="M9" s="17">
         <v>750</v>
       </c>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="18">
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17">
         <v>380</v>
       </c>
-      <c r="R9" s="18">
+      <c r="R9" s="17">
         <v>460</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="17">
         <v>35</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="17">
         <v>22.5</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <v>0.4</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="17">
         <v>25</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="17">
         <v>2.7</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="17">
         <v>4</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="17">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="25">
         <v>13000</v>
       </c>
-      <c r="J10" s="26">
+      <c r="J10" s="25">
         <v>8700</v>
       </c>
-      <c r="K10" s="18">
+      <c r="K10" s="17">
         <v>430</v>
       </c>
-      <c r="L10" s="18"/>
-      <c r="M10" s="18">
+      <c r="L10" s="17"/>
+      <c r="M10" s="17">
         <v>810</v>
       </c>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="18">
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17">
         <v>390</v>
       </c>
-      <c r="R10" s="18">
+      <c r="R10" s="17">
         <v>470</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="17">
         <v>40</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="17">
         <v>26</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="17">
         <v>0.4</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="17">
         <v>27</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <v>2.8</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="17">
         <v>4</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="17">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="25">
         <v>14000</v>
       </c>
-      <c r="J11" s="26">
+      <c r="J11" s="25">
         <v>9400</v>
       </c>
-      <c r="K11" s="18">
+      <c r="K11" s="17">
         <v>470</v>
       </c>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18">
+      <c r="L11" s="17"/>
+      <c r="M11" s="17">
         <v>880</v>
       </c>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="18">
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17">
         <v>400</v>
       </c>
-      <c r="R11" s="18">
+      <c r="R11" s="17">
         <v>480</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="17">
         <v>45</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="17">
         <v>30</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="17">
         <v>0.4</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="17">
         <v>29</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="17">
         <v>2.9</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="17">
         <v>4</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="17">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="25">
         <v>15000</v>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="25">
         <v>10100</v>
       </c>
-      <c r="K12" s="18">
+      <c r="K12" s="17">
         <v>500</v>
       </c>
-      <c r="L12" s="18"/>
-      <c r="M12" s="18">
+      <c r="L12" s="17"/>
+      <c r="M12" s="17">
         <v>940</v>
       </c>
-      <c r="N12" s="18"/>
-      <c r="O12" s="18"/>
-      <c r="P12" s="18"/>
-      <c r="Q12" s="18">
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17">
         <v>410</v>
       </c>
-      <c r="R12" s="18">
+      <c r="R12" s="17">
         <v>490</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="17">
         <v>50</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="17">
         <v>33.5</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="17">
         <v>0.4</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="17">
         <v>30</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="17">
         <v>3</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="17">
         <v>4</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="17">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="25">
         <v>16000</v>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="25">
         <v>10700</v>
       </c>
-      <c r="K13" s="18">
+      <c r="K13" s="17">
         <v>530</v>
       </c>
-      <c r="L13" s="18"/>
-      <c r="M13" s="18">
+      <c r="L13" s="17"/>
+      <c r="M13" s="17">
         <v>1000</v>
       </c>
-      <c r="N13" s="18"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="18">
+      <c r="N13" s="17"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="17">
         <v>430</v>
       </c>
-      <c r="R13" s="18">
+      <c r="R13" s="17">
         <v>520</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="20">
         <v>18</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="20">
         <v>11</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="20">
         <v>0.6</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="20">
         <v>18</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="20">
         <v>4.8</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="20">
         <v>3.5</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="20">
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="26">
         <v>9500</v>
       </c>
-      <c r="J14" s="27">
+      <c r="J14" s="26">
         <v>8000</v>
       </c>
-      <c r="K14" s="21">
+      <c r="K14" s="20">
         <v>630</v>
       </c>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21">
+      <c r="L14" s="20"/>
+      <c r="M14" s="20">
         <v>590</v>
       </c>
-      <c r="N14" s="21"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="21">
+      <c r="N14" s="20"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="20">
         <v>475</v>
       </c>
-      <c r="R14" s="21">
+      <c r="R14" s="20">
         <v>570</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="20">
         <v>24</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="20">
         <v>14</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="20">
         <v>0.6</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="20">
         <v>21</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="20">
         <v>4.9000000000000004</v>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="20">
         <v>3.7</v>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="20">
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
-      <c r="I15" s="27">
+      <c r="I15" s="26">
         <v>10000</v>
       </c>
-      <c r="J15" s="27">
+      <c r="J15" s="26">
         <v>8400</v>
       </c>
-      <c r="K15" s="21">
+      <c r="K15" s="20">
         <v>670</v>
       </c>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21">
+      <c r="L15" s="20"/>
+      <c r="M15" s="20">
         <v>630</v>
       </c>
-      <c r="N15" s="21"/>
-      <c r="O15" s="22"/>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="21">
+      <c r="N15" s="20"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="20">
         <v>485</v>
       </c>
-      <c r="R15" s="21">
+      <c r="R15" s="20">
         <v>580</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="20">
         <v>27</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="20">
         <v>16</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="20">
         <v>0.6</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="20">
         <v>22</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="20">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="20">
         <v>3.8</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="20">
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="26">
         <v>10500</v>
       </c>
-      <c r="J16" s="27">
+      <c r="J16" s="26">
         <v>8800</v>
       </c>
-      <c r="K16" s="21">
+      <c r="K16" s="20">
         <v>700</v>
       </c>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21">
+      <c r="L16" s="20"/>
+      <c r="M16" s="20">
         <v>660</v>
       </c>
-      <c r="N16" s="21"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="22"/>
-      <c r="Q16" s="21">
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="20">
         <v>510</v>
       </c>
-      <c r="R16" s="21">
+      <c r="R16" s="20">
         <v>610</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="20">
         <v>30</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="20">
         <v>18</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="20">
         <v>0.6</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="20">
         <v>24</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="20">
         <v>5.3</v>
       </c>
-      <c r="G17" s="21">
+      <c r="G17" s="20">
         <v>3.9</v>
       </c>
-      <c r="H17" s="21">
+      <c r="H17" s="20">
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="26">
         <v>11000</v>
       </c>
-      <c r="J17" s="27">
+      <c r="J17" s="26">
         <v>9200</v>
       </c>
-      <c r="K17" s="21">
+      <c r="K17" s="20">
         <v>730</v>
       </c>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21">
+      <c r="L17" s="20"/>
+      <c r="M17" s="20">
         <v>690</v>
       </c>
-      <c r="N17" s="21"/>
-      <c r="O17" s="22"/>
-      <c r="P17" s="22"/>
-      <c r="Q17" s="21">
+      <c r="N17" s="20"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="20">
         <v>530</v>
       </c>
-      <c r="R17" s="21">
+      <c r="R17" s="20">
         <v>640</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="20">
         <v>35</v>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="20">
         <v>21</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="20">
         <v>0.6</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="20">
         <v>25</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="20">
         <v>5.4</v>
       </c>
-      <c r="G18" s="21">
+      <c r="G18" s="20">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H18" s="21">
+      <c r="H18" s="20">
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
-      <c r="I18" s="27">
+      <c r="I18" s="26">
         <v>12000</v>
       </c>
-      <c r="J18" s="27">
+      <c r="J18" s="26">
         <v>10100</v>
       </c>
-      <c r="K18" s="21">
+      <c r="K18" s="20">
         <v>800</v>
       </c>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21">
+      <c r="L18" s="20"/>
+      <c r="M18" s="20">
         <v>750</v>
       </c>
-      <c r="N18" s="21"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="22"/>
-      <c r="Q18" s="21">
+      <c r="N18" s="20"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="20">
         <v>540</v>
       </c>
-      <c r="R18" s="21">
+      <c r="R18" s="20">
         <v>650</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="20">
         <v>40</v>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="20">
         <v>24</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="20">
         <v>0.6</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="20">
         <v>27</v>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="20">
         <v>5.5</v>
       </c>
-      <c r="G19" s="21">
+      <c r="G19" s="20">
         <v>4.2</v>
       </c>
-      <c r="H19" s="21">
+      <c r="H19" s="20">
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
-      <c r="I19" s="27">
+      <c r="I19" s="26">
         <v>13000</v>
       </c>
-      <c r="J19" s="27">
+      <c r="J19" s="26">
         <v>10900</v>
       </c>
-      <c r="K19" s="21">
+      <c r="K19" s="20">
         <v>870</v>
       </c>
-      <c r="L19" s="21"/>
-      <c r="M19" s="21">
+      <c r="L19" s="20"/>
+      <c r="M19" s="20">
         <v>810</v>
       </c>
-      <c r="N19" s="21"/>
-      <c r="O19" s="22"/>
-      <c r="P19" s="22"/>
-      <c r="Q19" s="21">
+      <c r="N19" s="20"/>
+      <c r="O19" s="21"/>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="20">
         <v>550</v>
       </c>
-      <c r="R19" s="21">
+      <c r="R19" s="20">
         <v>660</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="20">
         <v>45</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="20">
         <v>27</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="20">
         <v>0.6</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="20">
         <v>29</v>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="20">
         <v>5.8</v>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="20">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="20">
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
-      <c r="I20" s="27">
+      <c r="I20" s="26">
         <v>13500</v>
       </c>
-      <c r="J20" s="27">
+      <c r="J20" s="26">
         <v>11300</v>
       </c>
-      <c r="K20" s="21">
+      <c r="K20" s="20">
         <v>900</v>
       </c>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21">
+      <c r="L20" s="20"/>
+      <c r="M20" s="20">
         <v>840</v>
       </c>
-      <c r="N20" s="21"/>
-      <c r="O20" s="22"/>
-      <c r="P20" s="22"/>
-      <c r="Q20" s="21">
+      <c r="N20" s="20"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="20">
         <v>580</v>
       </c>
-      <c r="R20" s="21">
+      <c r="R20" s="20">
         <v>700</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="20">
         <v>50</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="20">
         <v>30</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="20">
         <v>0.6</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="20">
         <v>30</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="20">
         <v>6.2</v>
       </c>
-      <c r="G21" s="21">
+      <c r="G21" s="20">
         <v>4.5</v>
       </c>
-      <c r="H21" s="21">
+      <c r="H21" s="20">
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
-      <c r="I21" s="27">
+      <c r="I21" s="26">
         <v>14000</v>
       </c>
-      <c r="J21" s="27">
+      <c r="J21" s="26">
         <v>11800</v>
       </c>
-      <c r="K21" s="21">
+      <c r="K21" s="20">
         <v>930</v>
       </c>
-      <c r="L21" s="21"/>
-      <c r="M21" s="21">
+      <c r="L21" s="20"/>
+      <c r="M21" s="20">
         <v>880</v>
       </c>
-      <c r="N21" s="21"/>
-      <c r="O21" s="22"/>
-      <c r="P21" s="22"/>
-      <c r="Q21" s="21">
+      <c r="N21" s="20"/>
+      <c r="O21" s="21"/>
+      <c r="P21" s="21"/>
+      <c r="Q21" s="20">
         <v>620</v>
       </c>
-      <c r="R21" s="21">
+      <c r="R21" s="20">
         <v>740</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="20">
         <v>55</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="20">
         <v>33</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="20">
         <v>0.6</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="20">
         <v>32</v>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="20">
         <v>6.6</v>
       </c>
-      <c r="G22" s="21">
+      <c r="G22" s="20">
         <v>4.7</v>
       </c>
-      <c r="H22" s="21">
+      <c r="H22" s="20">
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
-      <c r="I22" s="27">
+      <c r="I22" s="26">
         <v>15500</v>
       </c>
-      <c r="J22" s="27">
+      <c r="J22" s="26">
         <v>13000</v>
       </c>
-      <c r="K22" s="21">
+      <c r="K22" s="20">
         <v>1030</v>
       </c>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21">
+      <c r="L22" s="20"/>
+      <c r="M22" s="20">
         <v>970</v>
       </c>
-      <c r="N22" s="21"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="22"/>
-      <c r="Q22" s="21">
+      <c r="N22" s="20"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="20">
         <v>660</v>
       </c>
-      <c r="R22" s="21">
+      <c r="R22" s="20">
         <v>790</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="20">
         <v>60</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="20">
         <v>36</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="20">
         <v>0.6</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="20">
         <v>33</v>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="20">
         <v>10.5</v>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="20">
         <v>4.8</v>
       </c>
-      <c r="H23" s="21">
+      <c r="H23" s="20">
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
-      <c r="I23" s="27">
+      <c r="I23" s="26">
         <v>17000</v>
       </c>
-      <c r="J23" s="27">
+      <c r="J23" s="26">
         <v>14300</v>
       </c>
-      <c r="K23" s="21">
+      <c r="K23" s="20">
         <v>1130</v>
       </c>
-      <c r="L23" s="21"/>
-      <c r="M23" s="21">
+      <c r="L23" s="20"/>
+      <c r="M23" s="20">
         <v>1060</v>
       </c>
-      <c r="N23" s="21"/>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
-      <c r="Q23" s="21">
+      <c r="N23" s="20"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="20">
         <v>700</v>
       </c>
-      <c r="R23" s="21">
+      <c r="R23" s="20">
         <v>840</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="B24" s="21">
+      <c r="B24" s="20">
         <v>65</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="20">
         <v>39</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="20">
         <v>0.6</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="20">
         <v>35</v>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="20">
         <v>11.3</v>
       </c>
-      <c r="G24" s="21">
+      <c r="G24" s="20">
         <v>5</v>
       </c>
-      <c r="H24" s="21">
+      <c r="H24" s="20">
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
-      <c r="I24" s="27">
+      <c r="I24" s="26">
         <v>18500</v>
       </c>
-      <c r="J24" s="27">
+      <c r="J24" s="26">
         <v>15500</v>
       </c>
-      <c r="K24" s="21">
+      <c r="K24" s="20">
         <v>1230</v>
       </c>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21">
+      <c r="L24" s="20"/>
+      <c r="M24" s="20">
         <v>1160</v>
       </c>
-      <c r="N24" s="21"/>
-      <c r="O24" s="22"/>
-      <c r="P24" s="22"/>
-      <c r="Q24" s="21">
+      <c r="N24" s="20"/>
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="20">
         <v>750</v>
       </c>
-      <c r="R24" s="21">
+      <c r="R24" s="20">
         <v>900</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="20">
         <v>70</v>
       </c>
-      <c r="C25" s="21">
+      <c r="C25" s="20">
         <v>42</v>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="20">
         <v>0.6</v>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="20">
         <v>36</v>
       </c>
-      <c r="F25" s="21">
+      <c r="F25" s="20">
         <v>12</v>
       </c>
-      <c r="G25" s="21">
+      <c r="G25" s="20">
         <v>5</v>
       </c>
-      <c r="H25" s="21">
+      <c r="H25" s="20">
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
-      <c r="I25" s="27">
+      <c r="I25" s="26">
         <v>20000</v>
       </c>
-      <c r="J25" s="27">
+      <c r="J25" s="26">
         <v>16800</v>
       </c>
-      <c r="K25" s="21">
+      <c r="K25" s="20">
         <v>1330</v>
       </c>
-      <c r="L25" s="21"/>
-      <c r="M25" s="21">
+      <c r="L25" s="20"/>
+      <c r="M25" s="20">
         <v>1250</v>
       </c>
-      <c r="N25" s="21"/>
-      <c r="O25" s="22"/>
-      <c r="P25" s="22"/>
-      <c r="Q25" s="21">
+      <c r="N25" s="20"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="20">
         <v>800</v>
       </c>
-      <c r="R25" s="21">
+      <c r="R25" s="20">
         <v>960</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="20">
         <v>75</v>
       </c>
-      <c r="C26" s="21">
+      <c r="C26" s="20">
         <v>45</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="20">
         <v>0.6</v>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="20">
         <v>37</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="20">
         <v>12.8</v>
       </c>
-      <c r="G26" s="21">
+      <c r="G26" s="20">
         <v>5</v>
       </c>
-      <c r="H26" s="21">
+      <c r="H26" s="20">
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
-      <c r="I26" s="27">
+      <c r="I26" s="26">
         <v>22000</v>
       </c>
-      <c r="J26" s="27">
+      <c r="J26" s="26">
         <v>18500</v>
       </c>
-      <c r="K26" s="21">
+      <c r="K26" s="20">
         <v>1470</v>
       </c>
-      <c r="L26" s="21"/>
-      <c r="M26" s="21">
+      <c r="L26" s="20"/>
+      <c r="M26" s="20">
         <v>1380</v>
       </c>
-      <c r="N26" s="21"/>
-      <c r="O26" s="22"/>
-      <c r="P26" s="22"/>
-      <c r="Q26" s="21">
+      <c r="N26" s="20"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="20">
         <v>850</v>
       </c>
-      <c r="R26" s="21">
+      <c r="R26" s="20">
         <v>1020</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="21">
+      <c r="B27" s="20">
         <v>80</v>
       </c>
-      <c r="C27" s="21">
+      <c r="C27" s="20">
         <v>48</v>
       </c>
-      <c r="D27" s="21">
+      <c r="D27" s="20">
         <v>0.6</v>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="20">
         <v>38</v>
       </c>
-      <c r="F27" s="21">
+      <c r="F27" s="20">
         <v>13.5</v>
       </c>
-      <c r="G27" s="21">
+      <c r="G27" s="20">
         <v>5</v>
       </c>
-      <c r="H27" s="21">
+      <c r="H27" s="20">
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
-      <c r="I27" s="27">
+      <c r="I27" s="26">
         <v>24000</v>
       </c>
-      <c r="J27" s="27">
+      <c r="J27" s="26">
         <v>20200</v>
       </c>
-      <c r="K27" s="21">
+      <c r="K27" s="20">
         <v>1600</v>
       </c>
-      <c r="L27" s="21"/>
-      <c r="M27" s="21">
+      <c r="L27" s="20"/>
+      <c r="M27" s="20">
         <v>1500</v>
       </c>
-      <c r="N27" s="21"/>
-      <c r="O27" s="22"/>
-      <c r="P27" s="22"/>
-      <c r="Q27" s="21">
+      <c r="N27" s="20"/>
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="20">
         <v>900</v>
       </c>
-      <c r="R27" s="21">
+      <c r="R27" s="20">
         <v>1080</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B28" s="23">
         <v>20</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="23">
         <v>15</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="23">
         <v>0.5</v>
       </c>
-      <c r="E28" s="24">
+      <c r="E28" s="23">
         <v>18.5</v>
       </c>
-      <c r="F28" s="24">
+      <c r="F28" s="23">
         <v>2.5</v>
       </c>
-      <c r="G28" s="24">
+      <c r="G28" s="23">
         <v>3.5</v>
       </c>
-      <c r="H28" s="24">
+      <c r="H28" s="23">
         <v>1.2</v>
       </c>
-      <c r="I28" s="28">
+      <c r="I28" s="27">
         <v>10400</v>
       </c>
-      <c r="J28" s="28">
+      <c r="J28" s="27">
         <v>8600</v>
       </c>
-      <c r="K28" s="24">
+      <c r="K28" s="23">
         <v>300</v>
       </c>
-      <c r="L28" s="24">
+      <c r="L28" s="23">
         <v>250</v>
       </c>
-      <c r="M28" s="24">
+      <c r="M28" s="23">
         <v>650</v>
       </c>
-      <c r="N28" s="24">
+      <c r="N28" s="23">
         <v>540</v>
       </c>
-      <c r="O28" s="24">
+      <c r="O28" s="23">
         <v>65</v>
       </c>
-      <c r="P28" s="24">
+      <c r="P28" s="23">
         <v>54</v>
       </c>
-      <c r="Q28" s="24">
+      <c r="Q28" s="23">
         <v>355</v>
       </c>
-      <c r="R28" s="24">
+      <c r="R28" s="23">
         <v>390</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B29" s="24">
+      <c r="B29" s="23">
         <v>22</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="23">
         <v>16</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="23">
         <v>0.5</v>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="23">
         <v>20</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="23">
         <v>2.5</v>
       </c>
-      <c r="G29" s="24">
+      <c r="G29" s="23">
         <v>3.5</v>
       </c>
-      <c r="H29" s="24">
+      <c r="H29" s="23">
         <v>1.2</v>
       </c>
-      <c r="I29" s="28">
+      <c r="I29" s="27">
         <v>10400</v>
       </c>
-      <c r="J29" s="28">
+      <c r="J29" s="27">
         <v>8600</v>
       </c>
-      <c r="K29" s="24">
+      <c r="K29" s="23">
         <v>300</v>
       </c>
-      <c r="L29" s="24">
+      <c r="L29" s="23">
         <v>250</v>
       </c>
-      <c r="M29" s="24">
+      <c r="M29" s="23">
         <v>650</v>
       </c>
-      <c r="N29" s="24">
+      <c r="N29" s="23">
         <v>540</v>
       </c>
-      <c r="O29" s="24">
+      <c r="O29" s="23">
         <v>65</v>
       </c>
-      <c r="P29" s="24">
+      <c r="P29" s="23">
         <v>54</v>
       </c>
-      <c r="Q29" s="24">
+      <c r="Q29" s="23">
         <v>355</v>
       </c>
-      <c r="R29" s="24">
+      <c r="R29" s="23">
         <v>390</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="24">
+      <c r="B30" s="23">
         <v>24</v>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="23">
         <v>17</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="23">
         <v>0.5</v>
       </c>
-      <c r="E30" s="24">
+      <c r="E30" s="23">
         <v>21.5</v>
       </c>
-      <c r="F30" s="24">
+      <c r="F30" s="23">
         <v>2.5</v>
       </c>
-      <c r="G30" s="24">
+      <c r="G30" s="23">
         <v>3.5</v>
       </c>
-      <c r="H30" s="24">
+      <c r="H30" s="23">
         <v>1.2</v>
       </c>
-      <c r="I30" s="28">
+      <c r="I30" s="27">
         <v>11000</v>
       </c>
-      <c r="J30" s="28">
+      <c r="J30" s="27">
         <v>9100</v>
       </c>
-      <c r="K30" s="24">
+      <c r="K30" s="23">
         <v>300</v>
       </c>
-      <c r="L30" s="24">
+      <c r="L30" s="23">
         <v>250</v>
       </c>
-      <c r="M30" s="24">
+      <c r="M30" s="23">
         <v>650</v>
       </c>
-      <c r="N30" s="24">
+      <c r="N30" s="23">
         <v>540</v>
       </c>
-      <c r="O30" s="24">
+      <c r="O30" s="23">
         <v>65</v>
       </c>
-      <c r="P30" s="24">
+      <c r="P30" s="23">
         <v>54</v>
       </c>
-      <c r="Q30" s="24">
+      <c r="Q30" s="23">
         <v>365</v>
       </c>
-      <c r="R30" s="24">
+      <c r="R30" s="23">
         <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="24">
+      <c r="B31" s="23">
         <v>26</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="23">
         <v>19</v>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="23">
         <v>0.5</v>
       </c>
-      <c r="E31" s="24">
+      <c r="E31" s="23">
         <v>23.5</v>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="23">
         <v>2.5</v>
       </c>
-      <c r="G31" s="24">
+      <c r="G31" s="23">
         <v>3.5</v>
       </c>
-      <c r="H31" s="24">
+      <c r="H31" s="23">
         <v>1.2</v>
       </c>
-      <c r="I31" s="28">
+      <c r="I31" s="27">
         <v>12000</v>
       </c>
-      <c r="J31" s="28">
+      <c r="J31" s="27">
         <v>10000</v>
       </c>
-      <c r="K31" s="24">
+      <c r="K31" s="23">
         <v>300</v>
       </c>
-      <c r="L31" s="24">
+      <c r="L31" s="23">
         <v>250</v>
       </c>
-      <c r="M31" s="24">
+      <c r="M31" s="23">
         <v>650</v>
       </c>
-      <c r="N31" s="24">
+      <c r="N31" s="23">
         <v>540</v>
       </c>
-      <c r="O31" s="24">
+      <c r="O31" s="23">
         <v>65</v>
       </c>
-      <c r="P31" s="24">
+      <c r="P31" s="23">
         <v>54</v>
       </c>
-      <c r="Q31" s="24">
+      <c r="Q31" s="23">
         <v>385</v>
       </c>
-      <c r="R31" s="24">
+      <c r="R31" s="23">
         <v>420</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" s="23" t="s">
+      <c r="A32" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B32" s="24">
+      <c r="B32" s="23">
         <v>28</v>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="23">
         <v>19.5</v>
       </c>
-      <c r="D32" s="24">
+      <c r="D32" s="23">
         <v>0.5</v>
       </c>
-      <c r="E32" s="24">
+      <c r="E32" s="23">
         <v>24</v>
       </c>
-      <c r="F32" s="24">
+      <c r="F32" s="23">
         <v>2.5</v>
       </c>
-      <c r="G32" s="24">
+      <c r="G32" s="23">
         <v>3.5</v>
       </c>
-      <c r="H32" s="24">
+      <c r="H32" s="23">
         <v>1.2</v>
       </c>
-      <c r="I32" s="28">
+      <c r="I32" s="27">
         <v>12500</v>
       </c>
-      <c r="J32" s="28">
+      <c r="J32" s="27">
         <v>10400</v>
       </c>
-      <c r="K32" s="24">
+      <c r="K32" s="23">
         <v>300</v>
       </c>
-      <c r="L32" s="24">
+      <c r="L32" s="23">
         <v>250</v>
       </c>
-      <c r="M32" s="24">
+      <c r="M32" s="23">
         <v>650</v>
       </c>
-      <c r="N32" s="24">
+      <c r="N32" s="23">
         <v>540</v>
       </c>
-      <c r="O32" s="24">
+      <c r="O32" s="23">
         <v>65</v>
       </c>
-      <c r="P32" s="24">
+      <c r="P32" s="23">
         <v>54</v>
       </c>
-      <c r="Q32" s="24">
+      <c r="Q32" s="23">
         <v>390</v>
       </c>
-      <c r="R32" s="24">
+      <c r="R32" s="23">
         <v>420</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="24">
+      <c r="B33" s="23">
         <v>30</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="23">
         <v>19.5</v>
       </c>
-      <c r="D33" s="24">
+      <c r="D33" s="23">
         <v>0.5</v>
       </c>
-      <c r="E33" s="24">
+      <c r="E33" s="23">
         <v>24.5</v>
       </c>
-      <c r="F33" s="24">
+      <c r="F33" s="23">
         <v>2.5</v>
       </c>
-      <c r="G33" s="24">
+      <c r="G33" s="23">
         <v>3.5</v>
       </c>
-      <c r="H33" s="24">
+      <c r="H33" s="23">
         <v>1.2</v>
       </c>
-      <c r="I33" s="28">
+      <c r="I33" s="27">
         <v>13000</v>
       </c>
-      <c r="J33" s="28">
+      <c r="J33" s="27">
         <v>10800</v>
       </c>
-      <c r="K33" s="24">
+      <c r="K33" s="23">
         <v>300</v>
       </c>
-      <c r="L33" s="24">
+      <c r="L33" s="23">
         <v>250</v>
       </c>
-      <c r="M33" s="24">
+      <c r="M33" s="23">
         <v>650</v>
       </c>
-      <c r="N33" s="24">
+      <c r="N33" s="23">
         <v>540</v>
       </c>
-      <c r="O33" s="24">
+      <c r="O33" s="23">
         <v>65</v>
       </c>
-      <c r="P33" s="24">
+      <c r="P33" s="23">
         <v>54</v>
       </c>
-      <c r="Q33" s="24">
+      <c r="Q33" s="23">
         <v>390</v>
       </c>
-      <c r="R33" s="24">
+      <c r="R33" s="23">
         <v>430</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" s="23" t="s">
+      <c r="A34" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="24">
+      <c r="B34" s="23">
         <v>32</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="23">
         <v>19.5</v>
       </c>
-      <c r="D34" s="24">
+      <c r="D34" s="23">
         <v>0.5</v>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="23">
         <v>24.5</v>
       </c>
-      <c r="F34" s="24">
+      <c r="F34" s="23">
         <v>2.5</v>
       </c>
-      <c r="G34" s="24">
+      <c r="G34" s="23">
         <v>3.5</v>
       </c>
-      <c r="H34" s="24">
+      <c r="H34" s="23">
         <v>1.2</v>
       </c>
-      <c r="I34" s="28">
+      <c r="I34" s="27">
         <v>13500</v>
       </c>
-      <c r="J34" s="28">
+      <c r="J34" s="27">
         <v>11200</v>
       </c>
-      <c r="K34" s="24">
+      <c r="K34" s="23">
         <v>300</v>
       </c>
-      <c r="L34" s="24">
+      <c r="L34" s="23">
         <v>250</v>
       </c>
-      <c r="M34" s="24">
+      <c r="M34" s="23">
         <v>650</v>
       </c>
-      <c r="N34" s="24">
+      <c r="N34" s="23">
         <v>540</v>
       </c>
-      <c r="O34" s="24">
+      <c r="O34" s="23">
         <v>65</v>
       </c>
-      <c r="P34" s="24">
+      <c r="P34" s="23">
         <v>54</v>
       </c>
-      <c r="Q34" s="24">
+      <c r="Q34" s="23">
         <v>400</v>
       </c>
-      <c r="R34" s="24">
+      <c r="R34" s="23">
         <v>440</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B35" s="24">
+      <c r="B35" s="23">
         <v>20</v>
       </c>
-      <c r="C35" s="24">
+      <c r="C35" s="23">
         <v>16</v>
       </c>
-      <c r="D35" s="24">
+      <c r="D35" s="23">
         <v>0.5</v>
       </c>
-      <c r="E35" s="24">
+      <c r="E35" s="23">
         <v>20</v>
       </c>
-      <c r="F35" s="24">
+      <c r="F35" s="23">
         <v>2.5</v>
       </c>
-      <c r="G35" s="24">
+      <c r="G35" s="23">
         <v>3.5</v>
       </c>
-      <c r="H35" s="24">
+      <c r="H35" s="23">
         <v>1.2</v>
       </c>
-      <c r="I35" s="28">
+      <c r="I35" s="27">
         <v>8400</v>
       </c>
-      <c r="J35" s="28">
+      <c r="J35" s="27">
         <v>7000</v>
       </c>
-      <c r="K35" s="24">
+      <c r="K35" s="23">
         <v>300</v>
       </c>
-      <c r="L35" s="24">
+      <c r="L35" s="23">
         <v>250</v>
       </c>
-      <c r="M35" s="24">
+      <c r="M35" s="23">
         <v>650</v>
       </c>
-      <c r="N35" s="24">
+      <c r="N35" s="23">
         <v>540</v>
       </c>
-      <c r="O35" s="24">
+      <c r="O35" s="23">
         <v>65</v>
       </c>
-      <c r="P35" s="24">
+      <c r="P35" s="23">
         <v>54</v>
       </c>
-      <c r="Q35" s="24">
+      <c r="Q35" s="23">
         <v>340</v>
       </c>
-      <c r="R35" s="24">
+      <c r="R35" s="23">
         <v>370</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B36" s="24">
+      <c r="B36" s="23">
         <v>22</v>
       </c>
-      <c r="C36" s="24">
+      <c r="C36" s="23">
         <v>17.600000000000001</v>
       </c>
-      <c r="D36" s="24">
+      <c r="D36" s="23">
         <v>0.5</v>
       </c>
-      <c r="E36" s="24">
+      <c r="E36" s="23">
         <v>22</v>
       </c>
-      <c r="F36" s="24">
+      <c r="F36" s="23">
         <v>2.5</v>
       </c>
-      <c r="G36" s="24">
+      <c r="G36" s="23">
         <v>3.5</v>
       </c>
-      <c r="H36" s="24">
+      <c r="H36" s="23">
         <v>1.2</v>
       </c>
-      <c r="I36" s="28">
+      <c r="I36" s="27">
         <v>10500</v>
       </c>
-      <c r="J36" s="28">
+      <c r="J36" s="27">
         <v>8800</v>
       </c>
-      <c r="K36" s="24">
+      <c r="K36" s="23">
         <v>300</v>
       </c>
-      <c r="L36" s="24">
+      <c r="L36" s="23">
         <v>250</v>
       </c>
-      <c r="M36" s="24">
+      <c r="M36" s="23">
         <v>650</v>
       </c>
-      <c r="N36" s="24">
+      <c r="N36" s="23">
         <v>540</v>
       </c>
-      <c r="O36" s="24">
+      <c r="O36" s="23">
         <v>65</v>
       </c>
-      <c r="P36" s="24">
+      <c r="P36" s="23">
         <v>54</v>
       </c>
-      <c r="Q36" s="24">
+      <c r="Q36" s="23">
         <v>370</v>
       </c>
-      <c r="R36" s="24">
+      <c r="R36" s="23">
         <v>410</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A37" s="23" t="s">
+      <c r="A37" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="24">
+      <c r="B37" s="23">
         <v>24</v>
       </c>
-      <c r="C37" s="24">
+      <c r="C37" s="23">
         <v>19.2</v>
       </c>
-      <c r="D37" s="24">
+      <c r="D37" s="23">
         <v>0.5</v>
       </c>
-      <c r="E37" s="24">
+      <c r="E37" s="23">
         <v>24</v>
       </c>
-      <c r="F37" s="24">
+      <c r="F37" s="23">
         <v>2.5</v>
       </c>
-      <c r="G37" s="24">
+      <c r="G37" s="23">
         <v>3.5</v>
       </c>
-      <c r="H37" s="24">
+      <c r="H37" s="23">
         <v>1.2</v>
       </c>
-      <c r="I37" s="28">
+      <c r="I37" s="27">
         <v>11500</v>
       </c>
-      <c r="J37" s="28">
+      <c r="J37" s="27">
         <v>9600</v>
       </c>
-      <c r="K37" s="24">
+      <c r="K37" s="23">
         <v>300</v>
       </c>
-      <c r="L37" s="24">
+      <c r="L37" s="23">
         <v>250</v>
       </c>
-      <c r="M37" s="24">
+      <c r="M37" s="23">
         <v>650</v>
       </c>
-      <c r="N37" s="24">
+      <c r="N37" s="23">
         <v>540</v>
       </c>
-      <c r="O37" s="24">
+      <c r="O37" s="23">
         <v>65</v>
       </c>
-      <c r="P37" s="24">
+      <c r="P37" s="23">
         <v>54</v>
       </c>
-      <c r="Q37" s="24">
+      <c r="Q37" s="23">
         <v>385</v>
       </c>
-      <c r="R37" s="24">
+      <c r="R37" s="23">
         <v>420</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A38" s="23" t="s">
+      <c r="A38" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="24">
+      <c r="B38" s="23">
         <v>26</v>
       </c>
-      <c r="C38" s="24">
+      <c r="C38" s="23">
         <v>20.8</v>
       </c>
-      <c r="D38" s="24">
+      <c r="D38" s="23">
         <v>0.5</v>
       </c>
-      <c r="E38" s="24">
+      <c r="E38" s="23">
         <v>26</v>
       </c>
-      <c r="F38" s="24">
+      <c r="F38" s="23">
         <v>2.5</v>
       </c>
-      <c r="G38" s="24">
+      <c r="G38" s="23">
         <v>3.5</v>
       </c>
-      <c r="H38" s="24">
+      <c r="H38" s="23">
         <v>1.2</v>
       </c>
-      <c r="I38" s="28">
+      <c r="I38" s="27">
         <v>12100</v>
       </c>
-      <c r="J38" s="28">
+      <c r="J38" s="27">
         <v>10100</v>
       </c>
-      <c r="K38" s="24">
+      <c r="K38" s="23">
         <v>300</v>
       </c>
-      <c r="L38" s="24">
+      <c r="L38" s="23">
         <v>250</v>
       </c>
-      <c r="M38" s="24">
+      <c r="M38" s="23">
         <v>650</v>
       </c>
-      <c r="N38" s="24">
+      <c r="N38" s="23">
         <v>540</v>
       </c>
-      <c r="O38" s="24">
+      <c r="O38" s="23">
         <v>65</v>
       </c>
-      <c r="P38" s="24">
+      <c r="P38" s="23">
         <v>54</v>
       </c>
-      <c r="Q38" s="24">
+      <c r="Q38" s="23">
         <v>405</v>
       </c>
-      <c r="R38" s="24">
+      <c r="R38" s="23">
         <v>445</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A39" s="23" t="s">
+      <c r="A39" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B39" s="24">
+      <c r="B39" s="23">
         <v>28</v>
       </c>
-      <c r="C39" s="24">
+      <c r="C39" s="23">
         <v>22.3</v>
       </c>
-      <c r="D39" s="24">
+      <c r="D39" s="23">
         <v>0.5</v>
       </c>
-      <c r="E39" s="24">
+      <c r="E39" s="23">
         <v>28</v>
       </c>
-      <c r="F39" s="24">
+      <c r="F39" s="23">
         <v>2.5</v>
       </c>
-      <c r="G39" s="24">
+      <c r="G39" s="23">
         <v>3.5</v>
       </c>
-      <c r="H39" s="24">
+      <c r="H39" s="23">
         <v>1.2</v>
       </c>
-      <c r="I39" s="28">
+      <c r="I39" s="27">
         <v>12600</v>
       </c>
-      <c r="J39" s="28">
+      <c r="J39" s="27">
         <v>10500</v>
       </c>
-      <c r="K39" s="24">
+      <c r="K39" s="23">
         <v>300</v>
       </c>
-      <c r="L39" s="24">
+      <c r="L39" s="23">
         <v>250</v>
       </c>
-      <c r="M39" s="24">
+      <c r="M39" s="23">
         <v>650</v>
       </c>
-      <c r="N39" s="24">
+      <c r="N39" s="23">
         <v>540</v>
       </c>
-      <c r="O39" s="24">
+      <c r="O39" s="23">
         <v>65</v>
       </c>
-      <c r="P39" s="24">
+      <c r="P39" s="23">
         <v>54</v>
       </c>
-      <c r="Q39" s="24">
+      <c r="Q39" s="23">
         <v>425</v>
       </c>
-      <c r="R39" s="24">
+      <c r="R39" s="23">
         <v>460</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40" s="23" t="s">
+      <c r="A40" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B40" s="24">
+      <c r="B40" s="23">
         <v>30</v>
       </c>
-      <c r="C40" s="24">
+      <c r="C40" s="23">
         <v>24</v>
       </c>
-      <c r="D40" s="24">
+      <c r="D40" s="23">
         <v>0.5</v>
       </c>
-      <c r="E40" s="24">
+      <c r="E40" s="23">
         <v>30</v>
       </c>
-      <c r="F40" s="24">
+      <c r="F40" s="23">
         <v>2.5</v>
       </c>
-      <c r="G40" s="24">
+      <c r="G40" s="23">
         <v>3.5</v>
       </c>
-      <c r="H40" s="24">
+      <c r="H40" s="23">
         <v>1.2</v>
       </c>
-      <c r="I40" s="28">
+      <c r="I40" s="27">
         <v>13600</v>
       </c>
-      <c r="J40" s="28">
+      <c r="J40" s="27">
         <v>11300</v>
       </c>
-      <c r="K40" s="24">
+      <c r="K40" s="23">
         <v>300</v>
       </c>
-      <c r="L40" s="24">
+      <c r="L40" s="23">
         <v>250</v>
       </c>
-      <c r="M40" s="24">
+      <c r="M40" s="23">
         <v>650</v>
       </c>
-      <c r="N40" s="24">
+      <c r="N40" s="23">
         <v>540</v>
       </c>
-      <c r="O40" s="24">
+      <c r="O40" s="23">
         <v>65</v>
       </c>
-      <c r="P40" s="24">
+      <c r="P40" s="23">
         <v>54</v>
       </c>
-      <c r="Q40" s="24">
+      <c r="Q40" s="23">
         <v>430</v>
       </c>
-      <c r="R40" s="24">
+      <c r="R40" s="23">
         <v>480</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A41" s="23" t="s">
+      <c r="A41" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B41" s="24">
+      <c r="B41" s="23">
         <v>32</v>
       </c>
-      <c r="C41" s="24">
+      <c r="C41" s="23">
         <v>25.6</v>
       </c>
-      <c r="D41" s="24">
+      <c r="D41" s="23">
         <v>0.5</v>
       </c>
-      <c r="E41" s="24">
+      <c r="E41" s="23">
         <v>32</v>
       </c>
-      <c r="F41" s="24">
+      <c r="F41" s="23">
         <v>2.5</v>
       </c>
-      <c r="G41" s="24">
+      <c r="G41" s="23">
         <v>3.5</v>
       </c>
-      <c r="H41" s="24">
+      <c r="H41" s="23">
         <v>1.2</v>
       </c>
-      <c r="I41" s="28">
+      <c r="I41" s="27">
         <v>14200</v>
       </c>
-      <c r="J41" s="28">
+      <c r="J41" s="27">
         <v>11800</v>
       </c>
-      <c r="K41" s="24">
+      <c r="K41" s="23">
         <v>300</v>
       </c>
-      <c r="L41" s="24">
+      <c r="L41" s="23">
         <v>250</v>
       </c>
-      <c r="M41" s="24">
+      <c r="M41" s="23">
         <v>650</v>
       </c>
-      <c r="N41" s="24">
+      <c r="N41" s="23">
         <v>540</v>
       </c>
-      <c r="O41" s="24">
+      <c r="O41" s="23">
         <v>65</v>
       </c>
-      <c r="P41" s="24">
+      <c r="P41" s="23">
         <v>54</v>
       </c>
-      <c r="Q41" s="24">
+      <c r="Q41" s="23">
         <v>440</v>
       </c>
-      <c r="R41" s="24">
+      <c r="R41" s="23">
         <v>490</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A42" s="68" t="s">
+      <c r="A42" s="64" t="s">
         <v>193</v>
       </c>
-      <c r="B42" s="69">
+      <c r="B42" s="65">
         <v>24</v>
       </c>
-      <c r="C42" s="69">
+      <c r="C42" s="65">
         <v>14.5</v>
       </c>
-      <c r="D42" s="69">
+      <c r="D42" s="65">
         <v>0.4</v>
       </c>
-      <c r="E42" s="69">
+      <c r="E42" s="65">
         <v>21</v>
       </c>
-      <c r="F42" s="69">
+      <c r="F42" s="65">
         <v>2.5</v>
       </c>
-      <c r="G42" s="69">
+      <c r="G42" s="65">
         <v>4</v>
       </c>
-      <c r="H42" s="69"/>
-      <c r="I42" s="70">
+      <c r="H42" s="65"/>
+      <c r="I42" s="66">
         <v>11000</v>
       </c>
-      <c r="J42" s="70">
+      <c r="J42" s="66">
         <v>7400</v>
       </c>
-      <c r="K42" s="69">
+      <c r="K42" s="65">
         <v>370</v>
       </c>
-      <c r="L42" s="69"/>
-      <c r="M42" s="69">
+      <c r="L42" s="65"/>
+      <c r="M42" s="65">
         <v>690</v>
       </c>
-      <c r="N42" s="69"/>
-      <c r="O42" s="69"/>
-      <c r="P42" s="69"/>
-      <c r="Q42" s="69">
+      <c r="N42" s="65"/>
+      <c r="O42" s="65"/>
+      <c r="P42" s="65"/>
+      <c r="Q42" s="65">
         <v>350</v>
       </c>
-      <c r="R42" s="69">
+      <c r="R42" s="65">
         <v>420</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A43" s="9"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="8"/>
+      <c r="A43" s="8"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
+      <c r="M43" s="7"/>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A44" s="9"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
+      <c r="A44" s="8"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="M44" s="6"/>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A45" s="9"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="7"/>
+      <c r="A45" s="8"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+      <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A46" s="9"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
+      <c r="A46" s="8"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A47" s="9"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="7"/>
+      <c r="A47" s="8"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="M47" s="6"/>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A48" s="9"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
+      <c r="A48" s="8"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="M48" s="6"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="9"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
+      <c r="A49" s="8"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="M49" s="6"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="9"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
+      <c r="A50" s="8"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="M50" s="6"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="9"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
+      <c r="A51" s="8"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="M51" s="6"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52" s="9"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
+      <c r="A52" s="8"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="M52" s="6"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A53" s="9"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="7"/>
-      <c r="K53" s="7"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="7"/>
+      <c r="A53" s="8"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="M53" s="6"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A54" s="9"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="7"/>
-      <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
+      <c r="A54" s="8"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="M54" s="6"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A55" s="9"/>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
-      <c r="K55" s="7"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
+      <c r="A55" s="8"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="M55" s="6"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A56" s="9"/>
+      <c r="A56" s="8"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
@@ -5683,7 +5661,7 @@
       <c r="M56" s="6"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A57" s="9"/>
+      <c r="A57" s="8"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
@@ -5696,18 +5674,18 @@
       <c r="M57" s="6"/>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A81" s="13"/>
+      <c r="A81" s="12"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
       <c r="G81" s="5"/>
-      <c r="H81" s="10"/>
-      <c r="I81" s="30"/>
-      <c r="J81" s="30"/>
+      <c r="H81" s="9"/>
+      <c r="I81" s="29"/>
+      <c r="J81" s="29"/>
       <c r="K81" s="4"/>
-      <c r="L81" s="9"/>
+      <c r="L81" s="8"/>
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
@@ -5718,89 +5696,89 @@
       <c r="T81" s="4"/>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A82" s="15"/>
+      <c r="A82" s="14"/>
       <c r="G82" s="1"/>
-      <c r="H82" s="16"/>
+      <c r="H82" s="15"/>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A83" s="15"/>
+      <c r="A83" s="14"/>
       <c r="G83" s="1"/>
-      <c r="H83" s="16"/>
+      <c r="H83" s="15"/>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A84" s="15"/>
+      <c r="A84" s="14"/>
       <c r="G84" s="1"/>
-      <c r="H84" s="16"/>
+      <c r="H84" s="15"/>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A85" s="15"/>
+      <c r="A85" s="14"/>
       <c r="G85" s="1"/>
-      <c r="H85" s="16"/>
+      <c r="H85" s="15"/>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A86" s="15"/>
+      <c r="A86" s="14"/>
       <c r="G86" s="1"/>
-      <c r="H86" s="16"/>
+      <c r="H86" s="15"/>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A87" s="15"/>
+      <c r="A87" s="14"/>
       <c r="G87" s="1"/>
-      <c r="H87" s="16"/>
+      <c r="H87" s="15"/>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A88" s="15"/>
+      <c r="A88" s="14"/>
       <c r="G88" s="1"/>
-      <c r="H88" s="16"/>
+      <c r="H88" s="15"/>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A89" s="15"/>
+      <c r="A89" s="14"/>
       <c r="G89" s="1"/>
-      <c r="H89" s="16"/>
+      <c r="H89" s="15"/>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A90" s="15"/>
+      <c r="A90" s="14"/>
       <c r="G90" s="1"/>
-      <c r="H90" s="16"/>
+      <c r="H90" s="15"/>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A91" s="15"/>
+      <c r="A91" s="14"/>
       <c r="G91" s="1"/>
-      <c r="H91" s="16"/>
+      <c r="H91" s="15"/>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A92" s="15"/>
+      <c r="A92" s="14"/>
       <c r="G92" s="1"/>
-      <c r="H92" s="16"/>
+      <c r="H92" s="15"/>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A93" s="15"/>
+      <c r="A93" s="14"/>
       <c r="G93" s="1"/>
-      <c r="H93" s="16"/>
+      <c r="H93" s="15"/>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A94" s="15"/>
+      <c r="A94" s="14"/>
       <c r="G94" s="1"/>
-      <c r="H94" s="16"/>
+      <c r="H94" s="15"/>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A95" s="15"/>
+      <c r="A95" s="14"/>
       <c r="G95" s="1"/>
-      <c r="H95" s="16"/>
+      <c r="H95" s="15"/>
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A96" s="15"/>
+      <c r="A96" s="14"/>
       <c r="G96" s="1"/>
-      <c r="H96" s="16"/>
+      <c r="H96" s="15"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="15"/>
+      <c r="A97" s="14"/>
       <c r="G97" s="1"/>
-      <c r="H97" s="16"/>
+      <c r="H97" s="15"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="15"/>
+      <c r="A98" s="14"/>
       <c r="G98" s="1"/>
-      <c r="H98" s="16"/>
+      <c r="H98" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5809,7 +5787,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6667,7 +6645,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6675,586 +6653,586 @@
     <col min="2" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
+    <row r="1" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="6">
         <v>14</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="6">
         <v>16</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <v>18</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="6">
         <v>20</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="6">
         <v>22</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="6">
         <v>24</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="6">
         <v>27</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="6">
         <v>30</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="6">
         <v>35</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="6">
         <v>40</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="6">
         <v>45</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="6">
         <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>7.2</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>8.5</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>10</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <v>11.5</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <v>13</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>14.5</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="6">
         <v>16.5</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="6">
         <v>19</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="6">
         <v>22.5</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="6">
         <v>26</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="6">
         <v>30</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="6">
         <v>33.5</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>0.4</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>0.4</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>0.4</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>0.4</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>0.4</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>0.4</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>0.4</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="6">
         <v>0.4</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="6">
         <v>0.4</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="6">
         <v>0.4</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="6">
         <v>0.4</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="6">
         <v>0.4</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>16</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>17</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>18</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>19</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <v>20</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="6">
         <v>21</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="6">
         <v>22</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="6">
         <v>24</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="6">
         <v>25</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="6">
         <v>27</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="6">
         <v>29</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="6">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>2</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <v>2.4</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="6">
         <v>2.5</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="6">
         <v>2.5</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="6">
         <v>2.7</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="6">
         <v>2.7</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="6">
         <v>2.8</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="6">
         <v>2.9</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="6">
         <v>3</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>3.2</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>3.4</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>3.6</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>3.8</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="6">
         <v>4</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="6">
         <v>4</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="6">
         <v>4</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="6">
         <v>4</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="6">
         <v>4</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="6">
         <v>4</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="6">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <f>2*B4</f>
         <v>0.8</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <f t="shared" ref="C8:M8" si="0">2*C4</f>
         <v>0.8</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="6">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="6">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="6">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="6">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="6">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="6">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="6">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>7</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>8</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <v>9</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>9.5</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <v>10</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="6">
         <v>11</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="6">
         <v>11.5</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="6">
         <v>12</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="6">
         <v>13</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="6">
         <v>14</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9" s="6">
         <v>15</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="6">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>4.7</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
         <v>5.4</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>6</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6">
         <v>6.4</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="6">
         <v>6.7</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="6">
         <v>7.4</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="6">
         <v>7.7</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="6">
         <v>8</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="6">
         <v>8.6999999999999993</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="6">
         <v>9.4</v>
       </c>
-      <c r="L10" s="7">
+      <c r="L10" s="6">
         <v>10.1</v>
       </c>
-      <c r="M10" s="7">
+      <c r="M10" s="6">
         <v>10.7</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>0.23</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>0.27</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>0.3</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>0.32</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <v>0.33</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="6">
         <v>0.37</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="6">
         <v>0.38</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="6">
         <v>0.4</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="6">
         <v>0.43</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="6">
         <v>0.47</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="6">
         <v>0.5</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="6">
         <v>0.53</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>0.44</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>0.5</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>0.56000000000000005</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="6">
         <v>0.59</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <v>0.63</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="6">
         <v>0.69</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="6">
         <v>0.72</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="6">
         <v>0.75</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="6">
         <v>0.81</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="6">
         <v>0.88</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="6">
         <v>0.94</v>
       </c>
-      <c r="M12" s="7">
+      <c r="M12" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="6">
         <v>290</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="6">
         <v>310</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>320</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6">
         <v>330</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <v>340</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="6">
         <v>350</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="6">
         <v>360</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="6">
         <v>380</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="6">
         <v>390</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13" s="6">
         <v>400</v>
       </c>
-      <c r="L13" s="7">
+      <c r="L13" s="6">
         <v>410</v>
       </c>
-      <c r="M13" s="7">
+      <c r="M13" s="6">
         <v>430</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="6">
         <v>350</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="6">
         <v>370</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>380</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="6">
         <v>390</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="6">
         <v>410</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="6">
         <v>420</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="6">
         <v>430</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="6">
         <v>460</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="6">
         <v>470</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="6">
         <v>480</v>
       </c>
-      <c r="L14" s="7">
+      <c r="L14" s="6">
         <v>490</v>
       </c>
-      <c r="M14" s="7">
+      <c r="M14" s="6">
         <v>520</v>
       </c>
     </row>
@@ -7265,107 +7243,107 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
+    <row r="1" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="S1" s="8" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="6">
         <v>13.5</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="6">
         <v>14.5</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <v>16</v>
       </c>
       <c r="E2" s="6">
         <v>17</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="6">
         <v>18</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="6">
         <v>19.5</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="6">
         <v>20.5</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="6">
         <v>21</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="6">
         <v>22</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="6">
         <v>23</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="6">
         <v>25.5</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="6">
         <v>29</v>
       </c>
       <c r="N2" s="6">
@@ -7388,43 +7366,43 @@
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>8</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>9</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>10</v>
       </c>
       <c r="E3" s="6">
         <v>11</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <v>12</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>13</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="6">
         <v>14</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="6">
         <v>14.5</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="6">
         <v>15</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="6">
         <v>16</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="6">
         <v>18</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="6">
         <v>21</v>
       </c>
       <c r="N3" s="6">
@@ -7447,43 +7425,43 @@
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>0.4</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>0.4</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>0.4</v>
       </c>
       <c r="E4" s="6">
         <v>0.4</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>0.4</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>0.4</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>0.4</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="6">
         <v>0.4</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="6">
         <v>0.4</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="6">
         <v>0.4</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="6">
         <v>0.4</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="6">
         <v>0.4</v>
       </c>
       <c r="N4" s="6">
@@ -7506,43 +7484,43 @@
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>16</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>17</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>17</v>
       </c>
       <c r="E5" s="6">
         <v>18</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <v>19</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="6">
         <v>20</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="6">
         <v>21</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="6">
         <v>21</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="6">
         <v>21</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="6">
         <v>22</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="6">
         <v>23</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="6">
         <v>25</v>
       </c>
       <c r="N5" s="6">
@@ -7565,43 +7543,43 @@
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>2</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>2.1</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>2.2000000000000002</v>
       </c>
       <c r="E6" s="6">
         <v>2.2000000000000002</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="6">
         <v>2.4</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="6">
         <v>2.5</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="6">
         <v>2.5</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="6">
         <v>2.5</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="6">
         <v>2.6</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="6">
         <v>2.7</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="6">
         <v>2.7</v>
       </c>
       <c r="N6" s="6">
@@ -7624,43 +7602,43 @@
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="6">
         <v>2.8</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>3</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>3.2</v>
       </c>
       <c r="E7" s="6">
         <v>3.4</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>3.6</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="6">
         <v>3.8</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="6">
         <v>4</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="6">
         <v>4</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="6">
         <v>4</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="6">
         <v>4</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="6">
         <v>4</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="6">
         <v>4</v>
       </c>
       <c r="N7" s="6">
@@ -7683,43 +7661,43 @@
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <v>7</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>7.5</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>8</v>
       </c>
       <c r="E8" s="6">
         <v>9</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>9.5</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="6">
         <v>10</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="6">
         <v>11</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="6">
         <v>11</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="6">
         <v>11.5</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="6">
         <v>11.5</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="6">
         <v>12</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="6">
         <v>13</v>
       </c>
       <c r="N8" s="6">
@@ -7742,43 +7720,43 @@
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>4.7</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>5</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <v>5.4</v>
       </c>
       <c r="E9" s="6">
         <v>6</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <v>6.4</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="6">
         <v>6.7</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="6">
         <v>7.4</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="6">
         <v>7.4</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="6">
         <v>7.7</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="6">
         <v>7.7</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9" s="6">
         <v>8</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="6">
         <v>8.6999999999999993</v>
       </c>
       <c r="N9" s="6">
@@ -7801,43 +7779,43 @@
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>0.23</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
         <v>0.25</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>0.27</v>
       </c>
       <c r="E10" s="6">
         <v>0.3</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="6">
         <v>0.32</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="6">
         <v>0.33</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="6">
         <v>0.37</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="6">
         <v>0.37</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="6">
         <v>0.38</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="6">
         <v>0.38</v>
       </c>
-      <c r="L10" s="7">
+      <c r="L10" s="6">
         <v>0.4</v>
       </c>
-      <c r="M10" s="7">
+      <c r="M10" s="6">
         <v>0.43</v>
       </c>
       <c r="N10" s="6">
@@ -7860,43 +7838,43 @@
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>0.44</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>0.47</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>0.5</v>
       </c>
       <c r="E11" s="6">
         <v>0.56000000000000005</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <v>0.59</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="6">
         <v>0.63</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="6">
         <v>0.69</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="6">
         <v>0.69</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="6">
         <v>0.72</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="6">
         <v>0.72</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="6">
         <v>0.75</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="6">
         <v>0.81</v>
       </c>
       <c r="N11" s="6">
@@ -7919,43 +7897,43 @@
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>290</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>300</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>310</v>
       </c>
       <c r="E12" s="6">
         <v>320</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <v>330</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="6">
         <v>340</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="6">
         <v>350</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="6">
         <v>350</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="6">
         <v>360</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="6">
         <v>370</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="6">
         <v>380</v>
       </c>
-      <c r="M12" s="7">
+      <c r="M12" s="6">
         <v>390</v>
       </c>
       <c r="N12" s="6">
@@ -7978,43 +7956,43 @@
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="6">
         <v>350</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="6">
         <v>360</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>370</v>
       </c>
       <c r="E13" s="6">
         <v>380</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <v>400</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="6">
         <v>410</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="6">
         <v>420</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="6">
         <v>420</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="6">
         <v>430</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13" s="6">
         <v>440</v>
       </c>
-      <c r="L13" s="7">
+      <c r="L13" s="6">
         <v>460</v>
       </c>
-      <c r="M13" s="7">
+      <c r="M13" s="6">
         <v>470</v>
       </c>
       <c r="N13" s="6">
@@ -8043,7 +8021,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8051,88 +8029,88 @@
     <col min="2" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
+    <row r="1" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="6">
         <v>18</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="6">
         <v>24</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <v>27</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="6">
         <v>30</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="6">
         <v>35</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="6">
         <v>40</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="6">
         <v>45</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="6">
         <v>50</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="6">
         <v>55</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="6">
         <v>60</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="6">
         <v>65</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="6">
         <v>70</v>
       </c>
       <c r="N2" s="6">
@@ -8143,43 +8121,43 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>11</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>14</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>16</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <v>18</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <v>21</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>24</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="6">
         <v>27</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="6">
         <v>30</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="6">
         <v>33</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="6">
         <v>36</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="6">
         <v>39</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="6">
         <v>42</v>
       </c>
       <c r="N3" s="6">
@@ -8190,43 +8168,43 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>0.6</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>0.6</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>0.6</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>0.6</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>0.6</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>0.6</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>0.6</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="6">
         <v>0.6</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="6">
         <v>0.6</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="6">
         <v>0.6</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="6">
         <v>0.6</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="6">
         <v>0.6</v>
       </c>
       <c r="N4" s="6">
@@ -8237,43 +8215,43 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>18</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>21</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>22</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>24</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <v>25</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="6">
         <v>27</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="6">
         <v>29</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="6">
         <v>30</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="6">
         <v>32</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="6">
         <v>33</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="6">
         <v>35</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="6">
         <v>36</v>
       </c>
       <c r="N5" s="6">
@@ -8284,43 +8262,43 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>4.8</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>4.9000000000000004</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>5.0999999999999996</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>5.3</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <v>5.4</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="6">
         <v>5.5</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="6">
         <v>5.8</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="6">
         <v>6.2</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="6">
         <v>6.6</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="6">
         <v>10.5</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="6">
         <v>11.3</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="6">
         <v>12</v>
       </c>
       <c r="N6" s="6">
@@ -8331,43 +8309,43 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="6">
         <v>3.5</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>3.7</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>3.8</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>3.9</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="6">
         <v>4.2</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="6">
         <v>4.4000000000000004</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="6">
         <v>4.5</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="6">
         <v>4.7</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="6">
         <v>4.8</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="6">
         <v>5</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="6">
         <v>5</v>
       </c>
       <c r="N7" s="6">
@@ -8378,43 +8356,43 @@
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <v>9.5</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>10</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>10.5</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <v>11</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>12</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="6">
         <v>13</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="6">
         <v>13.5</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="6">
         <v>14</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="6">
         <v>15.5</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="6">
         <v>17</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="6">
         <v>18.5</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="6">
         <v>20</v>
       </c>
       <c r="N8" s="6">
@@ -8425,43 +8403,43 @@
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>8</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>8.4</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <v>8.8000000000000007</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>9.1999999999999993</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <v>10.1</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="6">
         <v>10.9</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="6">
         <v>11.3</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="6">
         <v>11.8</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="6">
         <v>13</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="6">
         <v>14.3</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9" s="6">
         <v>15.5</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="6">
         <v>16.8</v>
       </c>
       <c r="N9" s="6">
@@ -8472,43 +8450,43 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>0.63</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
         <v>0.67</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>0.7</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6">
         <v>0.73</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="6">
         <v>0.8</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="6">
         <v>0.87</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="6">
         <v>0.9</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="6">
         <v>0.93</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="6">
         <v>1.03</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="6">
         <v>1.1299999999999999</v>
       </c>
-      <c r="L10" s="7">
+      <c r="L10" s="6">
         <v>1.23</v>
       </c>
-      <c r="M10" s="7">
+      <c r="M10" s="6">
         <v>1.33</v>
       </c>
       <c r="N10" s="6">
@@ -8519,43 +8497,43 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>0.59</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>0.63</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>0.66</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>0.69</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <v>0.75</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="6">
         <v>0.81</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="6">
         <v>0.84</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="6">
         <v>0.88</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="6">
         <v>0.97</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="6">
         <v>1.06</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="6">
         <v>1.1599999999999999</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="6">
         <v>1.25</v>
       </c>
       <c r="N11" s="6">
@@ -8566,43 +8544,43 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>475</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>485</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>510</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="6">
         <v>530</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <v>540</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="6">
         <v>550</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="6">
         <v>580</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="6">
         <v>620</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="6">
         <v>660</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="6">
         <v>700</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="6">
         <v>750</v>
       </c>
-      <c r="M12" s="7">
+      <c r="M12" s="6">
         <v>800</v>
       </c>
       <c r="N12" s="6">
@@ -8613,43 +8591,43 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="6">
         <v>570</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="6">
         <v>580</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>610</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6">
         <v>640</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <v>650</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="6">
         <v>660</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="6">
         <v>700</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="6">
         <v>740</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="6">
         <v>790</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13" s="6">
         <v>840</v>
       </c>
-      <c r="L13" s="7">
+      <c r="L13" s="6">
         <v>900</v>
       </c>
-      <c r="M13" s="7">
+      <c r="M13" s="6">
         <v>960</v>
       </c>
       <c r="N13" s="6">

--- a/NODELibrary/Data/Materialdata.xlsx
+++ b/NODELibrary/Data/Materialdata.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\NODEMaple\NODELibrary\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56B9C34-7C75-40C7-AB7F-6D4D4C969952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{107753C5-EAA1-4006-9436-FABDD1C4FC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="18240" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LESMEG" sheetId="5" r:id="rId1"/>
     <sheet name="concrete" sheetId="4" r:id="rId2"/>
     <sheet name="steel" sheetId="6" r:id="rId3"/>
-    <sheet name="tre" sheetId="3" r:id="rId4"/>
+    <sheet name="timber" sheetId="3" r:id="rId4"/>
     <sheet name="limtre" sheetId="1" r:id="rId5"/>
     <sheet name="softwood" sheetId="2" r:id="rId6"/>
     <sheet name="softwood tension tests" sheetId="7" r:id="rId7"/>
